--- a/Selva Viva/celulosa_bulk_final.xlsx
+++ b/Selva Viva/celulosa_bulk_final.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="todo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="pendientes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="resumen" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="todo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pendientes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z153"/>
+  <dimension ref="A1:Z149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6694,10 +6694,10 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>52.1703514062085</v>
+        <v>0.4488</v>
       </c>
       <c r="L69" t="n">
-        <v>-31.974735763936</v>
+        <v>-30.83</v>
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
@@ -6780,10 +6780,10 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>0.4488</v>
+        <v>52.1703514062085</v>
       </c>
       <c r="L70" t="n">
-        <v>-30.83</v>
+        <v>-31.974735763936</v>
       </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -8387,15 +8387,23 @@
       <c r="L88" t="n">
         <v>-29.77</v>
       </c>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
+      <c r="M88" t="n">
+        <v>0.01245650406992576</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.4623296600125005</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.2163299630070622</v>
+      </c>
+      <c r="P88" t="n">
+        <v>-32.72903641196186</v>
+      </c>
       <c r="Q88" t="b">
         <v>0</v>
       </c>
       <c r="R88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S88" t="b">
         <v>0</v>
@@ -8408,12 +8416,12 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>pesar bulk</t>
+          <t>completo</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>68-8869</t>
+          <t>p68-8869</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
@@ -9020,7 +9028,7 @@
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>9865</v>
+        <v>8865</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
@@ -9042,15 +9050,23 @@
       <c r="L96" t="n">
         <v>-32.9258451761764</v>
       </c>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
+      <c r="M96" t="n">
+        <v>0.02234992814914083</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.4489033340843991</v>
+      </c>
+      <c r="O96" t="n">
+        <v>2.108676665915091</v>
+      </c>
+      <c r="P96" t="n">
+        <v>-33.46661356502295</v>
+      </c>
       <c r="Q96" t="b">
         <v>0</v>
       </c>
       <c r="R96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S96" t="b">
         <v>0</v>
@@ -9063,12 +9079,12 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>pesar bulk; falta familia</t>
+          <t>falta familia</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>68-9865</t>
+          <t>p68-8865</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
@@ -9080,40 +9096,56 @@
       <c r="Z96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>8865</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
+      <c r="A97" t="n">
+        <v>2167</v>
+      </c>
+      <c r="B97" t="n">
+        <v>3609</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Euphorbiaceae</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Pseudosenefeldera</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>inclinata</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H97" t="n">
         <v>2025</v>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
+      <c r="K97" t="n">
+        <v>42.2153607736312</v>
+      </c>
+      <c r="L97" t="n">
+        <v>-30.6732666344141</v>
+      </c>
       <c r="M97" t="n">
-        <v>0.02234992814914083</v>
+        <v>0.02341087029895825</v>
       </c>
       <c r="N97" t="n">
-        <v>0.4489033340843991</v>
+        <v>0.433943697942952</v>
       </c>
       <c r="O97" t="n">
-        <v>2.108676665915091</v>
+        <v>-0.63</v>
       </c>
       <c r="P97" t="n">
-        <v>-33.46661356502295</v>
+        <v>-32.26</v>
       </c>
       <c r="Q97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" t="b">
         <v>0</v>
@@ -9122,19 +9154,19 @@
         <v>0</v>
       </c>
       <c r="T97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>pesar celulosa; falta familia</t>
+          <t>completo</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>p68-8865</t>
+          <t>p69-3609</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
@@ -9142,44 +9174,68 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>p69-3609</t>
+        </is>
+      </c>
       <c r="Z97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>8869</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+      <c r="A98" t="n">
+        <v>2171</v>
+      </c>
+      <c r="B98" t="n">
+        <v>3605</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Moraceae</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Ficus</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>pulchella</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>3841</t>
+        </is>
+      </c>
       <c r="G98" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H98" t="n">
         <v>2025</v>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
+      <c r="K98" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="L98" t="n">
+        <v>-29.27</v>
+      </c>
       <c r="M98" t="n">
-        <v>0.01245650406992576</v>
+        <v>0.02213145516022583</v>
       </c>
       <c r="N98" t="n">
-        <v>0.4623296600125005</v>
+        <v>0.4282614261488554</v>
       </c>
       <c r="O98" t="n">
-        <v>0.2163299630070622</v>
+        <v>0.46</v>
       </c>
       <c r="P98" t="n">
-        <v>-32.72903641196186</v>
+        <v>-31.85</v>
       </c>
       <c r="Q98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="b">
         <v>0</v>
@@ -9188,19 +9244,19 @@
         <v>0</v>
       </c>
       <c r="T98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>pesar celulosa; falta familia</t>
+          <t>completo</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>p68-8869</t>
+          <t>p69-3605</t>
         </is>
       </c>
       <c r="X98" t="inlineStr">
@@ -9208,32 +9264,40 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>p69-3605</t>
+        </is>
+      </c>
       <c r="Z98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2167</v>
+        <v>2171</v>
       </c>
       <c r="B99" t="n">
-        <v>3609</v>
+        <v>3605</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Euphorbiaceae</t>
+          <t>Moraceae</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Pseudosenefeldera</t>
+          <t>Ficus</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>inclinata</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
+          <t>pulchella</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>3841</t>
+        </is>
+      </c>
       <c r="G99" t="n">
         <v>69</v>
       </c>
@@ -9243,22 +9307,22 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="n">
-        <v>42.2153607736312</v>
+        <v>34.9329096455498</v>
       </c>
       <c r="L99" t="n">
-        <v>-30.6732666344141</v>
+        <v>-29.1899606205167</v>
       </c>
       <c r="M99" t="n">
-        <v>0.02341087029895825</v>
+        <v>0.02213145516022583</v>
       </c>
       <c r="N99" t="n">
-        <v>0.433943697942952</v>
+        <v>0.4282614261488554</v>
       </c>
       <c r="O99" t="n">
-        <v>-0.63</v>
+        <v>0.46</v>
       </c>
       <c r="P99" t="n">
-        <v>-32.26</v>
+        <v>-31.85</v>
       </c>
       <c r="Q99" t="b">
         <v>0</v>
@@ -9282,7 +9346,7 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>p69-3609</t>
+          <t>p69-3605</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
@@ -9292,17 +9356,17 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>p69-3609</t>
+          <t>p69-3605</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="B100" t="n">
-        <v>3605</v>
+        <v>3606</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -9311,17 +9375,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Ficus</t>
+          <t>Batocarpus</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>pulchella</t>
+          <t>orinocensis</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -9333,22 +9397,22 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="n">
-        <v>0.3583</v>
+        <v>45.5937982420793</v>
       </c>
       <c r="L100" t="n">
-        <v>-29.27</v>
+        <v>-30.7104219532734</v>
       </c>
       <c r="M100" t="n">
-        <v>0.02213145516022583</v>
+        <v>0.02485796670088971</v>
       </c>
       <c r="N100" t="n">
-        <v>0.4282614261488554</v>
+        <v>0.4378430142968719</v>
       </c>
       <c r="O100" t="n">
-        <v>0.46</v>
+        <v>0.12</v>
       </c>
       <c r="P100" t="n">
-        <v>-31.85</v>
+        <v>-31.98</v>
       </c>
       <c r="Q100" t="b">
         <v>0</v>
@@ -9372,7 +9436,7 @@
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>p69-3605</t>
+          <t>p69-3606</t>
         </is>
       </c>
       <c r="X100" t="inlineStr">
@@ -9382,36 +9446,36 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>p69-3605</t>
+          <t>p69-3606</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2171</v>
+        <v>2177</v>
       </c>
       <c r="B101" t="n">
-        <v>3605</v>
+        <v>3617</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>Fabaceae</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Ficus</t>
+          <t>Browneopsis</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>pulchella</t>
+          <t>ucayalina</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -9423,22 +9487,22 @@
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="n">
-        <v>34.9329096455498</v>
+        <v>42.5482890591904</v>
       </c>
       <c r="L101" t="n">
-        <v>-29.1899606205167</v>
+        <v>-30.1388182040637</v>
       </c>
       <c r="M101" t="n">
-        <v>0.02213145516022583</v>
+        <v>0.01853964833900083</v>
       </c>
       <c r="N101" t="n">
-        <v>0.4282614261488554</v>
+        <v>0.4430114955907127</v>
       </c>
       <c r="O101" t="n">
-        <v>0.46</v>
+        <v>2.34</v>
       </c>
       <c r="P101" t="n">
-        <v>-31.85</v>
+        <v>-32.61</v>
       </c>
       <c r="Q101" t="b">
         <v>0</v>
@@ -9462,7 +9526,7 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>p69-3605</t>
+          <t>p69-8617</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
@@ -9472,38 +9536,34 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>p69-3605</t>
+          <t>p69-8617</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2172</v>
+        <v>2179</v>
       </c>
       <c r="B102" t="n">
-        <v>3606</v>
+        <v>3619</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>Salicaceae</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Batocarpus</t>
+          <t>Tetrathylacium</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>orinocensis</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>3842</t>
-        </is>
-      </c>
+          <t>macrophyllum</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
         <v>69</v>
       </c>
@@ -9513,22 +9573,22 @@
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="n">
-        <v>45.5937982420793</v>
+        <v>43.2832197782582</v>
       </c>
       <c r="L102" t="n">
-        <v>-30.7104219532734</v>
+        <v>-32.3631333555326</v>
       </c>
       <c r="M102" t="n">
-        <v>0.02485796670088971</v>
+        <v>0.01915534221097701</v>
       </c>
       <c r="N102" t="n">
-        <v>0.4378430142968719</v>
+        <v>0.4350616092673997</v>
       </c>
       <c r="O102" t="n">
-        <v>0.12</v>
+        <v>-0.12</v>
       </c>
       <c r="P102" t="n">
-        <v>-31.98</v>
+        <v>-34.07</v>
       </c>
       <c r="Q102" t="b">
         <v>0</v>
@@ -9552,7 +9612,7 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>p69-3606</t>
+          <t>p69-3619</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
@@ -9562,31 +9622,31 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>p69-3606</t>
+          <t>p69-3619</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="B103" t="n">
-        <v>3619</v>
+        <v>3612</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Salicaceae</t>
+          <t>Myristicaceae</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Tetrathylacium</t>
+          <t>Otoba</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>macrophyllum</t>
+          <t>parvifolia</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -9599,22 +9659,22 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="n">
-        <v>43.2832197782582</v>
+        <v>49.475400021233</v>
       </c>
       <c r="L103" t="n">
-        <v>-32.3631333555326</v>
+        <v>-30.3754078922675</v>
       </c>
       <c r="M103" t="n">
-        <v>0.01915534221097701</v>
+        <v>0.0144700480896215</v>
       </c>
       <c r="N103" t="n">
-        <v>0.4350616092673997</v>
+        <v>0.4792818843283498</v>
       </c>
       <c r="O103" t="n">
-        <v>-0.12</v>
+        <v>-0.86</v>
       </c>
       <c r="P103" t="n">
-        <v>-34.07</v>
+        <v>-31.62</v>
       </c>
       <c r="Q103" t="b">
         <v>0</v>
@@ -9638,7 +9698,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>p69-3619</t>
+          <t>p69-3612</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
@@ -9648,34 +9708,38 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>p69-3619</t>
+          <t>p69-3612</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2180</v>
+        <v>2184</v>
       </c>
       <c r="B104" t="n">
-        <v>3612</v>
+        <v>8892</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Myristicaceae</t>
+          <t>Rubiaceae</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Otoba</t>
+          <t>Pentagonia</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>parvifolia</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
+          <t>amazonica</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>3847</t>
+        </is>
+      </c>
       <c r="G104" t="n">
         <v>69</v>
       </c>
@@ -9685,22 +9749,22 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="n">
-        <v>49.475400021233</v>
+        <v>42.8070573375508</v>
       </c>
       <c r="L104" t="n">
-        <v>-30.3754078922675</v>
+        <v>-32.6885972072656</v>
       </c>
       <c r="M104" t="n">
-        <v>0.0144700480896215</v>
+        <v>0.01810419616968846</v>
       </c>
       <c r="N104" t="n">
-        <v>0.4792818843283498</v>
+        <v>0.4657246583502926</v>
       </c>
       <c r="O104" t="n">
-        <v>-0.86</v>
+        <v>2.56</v>
       </c>
       <c r="P104" t="n">
-        <v>-31.62</v>
+        <v>-34.8</v>
       </c>
       <c r="Q104" t="b">
         <v>0</v>
@@ -9724,7 +9788,7 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>p69-3612</t>
+          <t>p69-8892</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
@@ -9734,36 +9798,36 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>p69-3612</t>
+          <t>p69-8892</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="B105" t="n">
-        <v>8892</v>
+        <v>8891</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
+          <t>Sapindaceae</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Pentagonia</t>
+          <t>Allophylus</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>amazonica</t>
+          <t>punctatus</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -9775,22 +9839,22 @@
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="n">
-        <v>42.8070573375508</v>
+        <v>42.1646348035949</v>
       </c>
       <c r="L105" t="n">
-        <v>-32.6885972072656</v>
+        <v>-32.95862784708</v>
       </c>
       <c r="M105" t="n">
-        <v>0.01810419616968846</v>
+        <v>0.02990649007833678</v>
       </c>
       <c r="N105" t="n">
-        <v>0.4657246583502926</v>
+        <v>0.442290096180273</v>
       </c>
       <c r="O105" t="n">
-        <v>2.56</v>
+        <v>-0.03</v>
       </c>
       <c r="P105" t="n">
-        <v>-34.8</v>
+        <v>-35.22</v>
       </c>
       <c r="Q105" t="b">
         <v>0</v>
@@ -9814,7 +9878,7 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>p69-8892</t>
+          <t>p69-8891</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
@@ -9824,36 +9888,36 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>p69-8892</t>
+          <t>p69-8891</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2185</v>
+        <v>2190</v>
       </c>
       <c r="B106" t="n">
-        <v>8891</v>
+        <v>8899</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sapindaceae</t>
+          <t>Lacistemataceae</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Allophylus</t>
+          <t>Lozania</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>punctatus</t>
+          <t>klugii</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -9862,25 +9926,27 @@
       <c r="H106" t="n">
         <v>2025</v>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="n">
+        <v>8899</v>
+      </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="n">
-        <v>42.1646348035949</v>
+        <v>45.58</v>
       </c>
       <c r="L106" t="n">
-        <v>-32.95862784708</v>
+        <v>-31.71</v>
       </c>
       <c r="M106" t="n">
-        <v>0.02990649007833678</v>
+        <v>0.02424633156897932</v>
       </c>
       <c r="N106" t="n">
-        <v>0.442290096180273</v>
+        <v>0.458128613555163</v>
       </c>
       <c r="O106" t="n">
-        <v>-0.03</v>
+        <v>1.196791821189593</v>
       </c>
       <c r="P106" t="n">
-        <v>-35.22</v>
+        <v>-33.40482562381237</v>
       </c>
       <c r="Q106" t="b">
         <v>0</v>
@@ -9904,7 +9970,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>p69-8891</t>
+          <t>p69-8899</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
@@ -9912,67 +9978,57 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>p69-8891</t>
-        </is>
-      </c>
+      <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="B107" t="n">
-        <v>8899</v>
+        <v>8898</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Lacistemataceae</t>
+          <t>Euphorbiaceae</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Lozania</t>
+          <t>Pseudosenefeldera</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>klugii</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>3850</t>
-        </is>
-      </c>
+          <t>inclinata</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
         <v>69</v>
       </c>
       <c r="H107" t="n">
         <v>2025</v>
       </c>
-      <c r="I107" t="n">
-        <v>8899</v>
-      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="n">
-        <v>45.58</v>
+        <v>41.0106971326434</v>
       </c>
       <c r="L107" t="n">
-        <v>-31.71</v>
+        <v>-31.2602916893349</v>
       </c>
       <c r="M107" t="n">
-        <v>0.02424633156897932</v>
+        <v>0.02685294930046833</v>
       </c>
       <c r="N107" t="n">
-        <v>0.458128613555163</v>
+        <v>0.4356585352943561</v>
       </c>
       <c r="O107" t="n">
-        <v>1.196791821189593</v>
+        <v>0.66</v>
       </c>
       <c r="P107" t="n">
-        <v>-33.40482562381237</v>
+        <v>-33.2</v>
       </c>
       <c r="Q107" t="b">
         <v>0</v>
@@ -9996,7 +10052,7 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>p69-8899</t>
+          <t>p69-8898</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
@@ -10004,32 +10060,40 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y107" t="inlineStr"/>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>p69-8898</t>
+        </is>
+      </c>
       <c r="Z107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2191</v>
+        <v>2195</v>
       </c>
       <c r="B108" t="n">
-        <v>8898</v>
+        <v>8895</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Euphorbiaceae</t>
+          <t>Celastraceae</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Pseudosenefeldera</t>
+          <t>Salacia</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>inclinata</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
+          <t>aff. cordata</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>3852</t>
+        </is>
+      </c>
       <c r="G108" t="n">
         <v>69</v>
       </c>
@@ -10039,22 +10103,22 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="n">
-        <v>41.0106971326434</v>
+        <v>48.7370403004821</v>
       </c>
       <c r="L108" t="n">
-        <v>-31.2602916893349</v>
+        <v>-35.0508631508533</v>
       </c>
       <c r="M108" t="n">
-        <v>0.02685294930046833</v>
+        <v>0.02466862000311886</v>
       </c>
       <c r="N108" t="n">
-        <v>0.4356585352943561</v>
+        <v>0.4874293332468896</v>
       </c>
       <c r="O108" t="n">
-        <v>0.66</v>
+        <v>2.82</v>
       </c>
       <c r="P108" t="n">
-        <v>-33.2</v>
+        <v>-36.94</v>
       </c>
       <c r="Q108" t="b">
         <v>0</v>
@@ -10078,7 +10142,7 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>p69-8898</t>
+          <t>p69-8895</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
@@ -10088,36 +10152,36 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>p69-8898</t>
+          <t>p69-8895</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="B109" t="n">
-        <v>8895</v>
+        <v>8894</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Celastraceae</t>
+          <t>Moraceae</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Salacia</t>
+          <t>Brosimum</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>aff. cordata</t>
+          <t>lactescens</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -10126,25 +10190,27 @@
       <c r="H109" t="n">
         <v>2025</v>
       </c>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="n">
+        <v>8894</v>
+      </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="n">
-        <v>48.7370403004821</v>
+        <v>46.54</v>
       </c>
       <c r="L109" t="n">
-        <v>-35.0508631508533</v>
+        <v>-30.79</v>
       </c>
       <c r="M109" t="n">
-        <v>0.02466862000311886</v>
+        <v>0.01844715935121516</v>
       </c>
       <c r="N109" t="n">
-        <v>0.4874293332468896</v>
+        <v>0.4404883832314956</v>
       </c>
       <c r="O109" t="n">
-        <v>2.82</v>
+        <v>2.494400036023943</v>
       </c>
       <c r="P109" t="n">
-        <v>-36.94</v>
+        <v>-32.13088081399432</v>
       </c>
       <c r="Q109" t="b">
         <v>0</v>
@@ -10168,7 +10234,7 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>p69-8895</t>
+          <t>p69-8894</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
@@ -10176,19 +10242,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>p69-8895</t>
-        </is>
-      </c>
+      <c r="Y109" t="inlineStr"/>
       <c r="Z109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="B110" t="n">
-        <v>8894</v>
+        <v>8893</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -10197,17 +10259,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Brosimum</t>
+          <t>Pseudolmedia</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>lactescens</t>
+          <t>macrophylla</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -10217,26 +10279,26 @@
         <v>2025</v>
       </c>
       <c r="I110" t="n">
-        <v>8894</v>
+        <v>8893</v>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="n">
-        <v>46.54</v>
+        <v>43.4988316896495</v>
       </c>
       <c r="L110" t="n">
-        <v>-30.79</v>
+        <v>-33.7079403532742</v>
       </c>
       <c r="M110" t="n">
-        <v>0.01844715935121516</v>
+        <v>0.0140003582445462</v>
       </c>
       <c r="N110" t="n">
-        <v>0.4404883832314956</v>
+        <v>0.3883734423353893</v>
       </c>
       <c r="O110" t="n">
-        <v>2.494400036023943</v>
+        <v>0.8692445291019997</v>
       </c>
       <c r="P110" t="n">
-        <v>-32.13088081399432</v>
+        <v>-35.5916730458568</v>
       </c>
       <c r="Q110" t="b">
         <v>0</v>
@@ -10260,7 +10322,7 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>p69-8894</t>
+          <t>p69-8893</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
@@ -10273,56 +10335,60 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2199</v>
+        <v>2202</v>
       </c>
       <c r="B111" t="n">
-        <v>8893</v>
+        <v>3658</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>Achariaceae</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Pseudolmedia</t>
+          <t>Lindackeria</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>macrophylla</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>3855</t>
-        </is>
+          <t>paludosa</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>3873</v>
       </c>
       <c r="G111" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H111" t="n">
         <v>2025</v>
       </c>
-      <c r="I111" t="n">
-        <v>8893</v>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="n">
-        <v>43.4988316896495</v>
+        <v>40.7185817747011</v>
       </c>
       <c r="L111" t="n">
-        <v>-33.7079403532742</v>
-      </c>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
+        <v>-31.5051012323677</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.022130638</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.436691485</v>
+      </c>
+      <c r="O111" t="n">
+        <v>2.122085858585857</v>
+      </c>
+      <c r="P111" t="n">
+        <v>-33.32435503711559</v>
+      </c>
       <c r="Q111" t="b">
         <v>0</v>
       </c>
       <c r="R111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S111" t="b">
         <v>0</v>
@@ -10335,12 +10401,12 @@
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>pesar bulk</t>
+          <t>completo</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>69-8893</t>
+          <t>p70-3658</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
@@ -10348,43 +10414,65 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y111" t="inlineStr"/>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>p70-3658</t>
+        </is>
+      </c>
       <c r="Z111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
+      <c r="A112" t="n">
+        <v>2202</v>
+      </c>
       <c r="B112" t="n">
-        <v>8617</v>
-      </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+        <v>3658</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Achariaceae</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Lindackeria</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>paludosa</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>3873</v>
+      </c>
       <c r="G112" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H112" t="n">
         <v>2025</v>
       </c>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="n">
+        <v>3658</v>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="n">
-        <v>42.5482890591904</v>
+        <v>45.45</v>
       </c>
       <c r="L112" t="n">
-        <v>-30.1388182040637</v>
+        <v>-32.26</v>
       </c>
       <c r="M112" t="n">
-        <v>0.01853964833900083</v>
+        <v>0.022130638</v>
       </c>
       <c r="N112" t="n">
-        <v>0.4430114955907127</v>
+        <v>0.436691485</v>
       </c>
       <c r="O112" t="n">
-        <v>2.34</v>
+        <v>2.122085858585857</v>
       </c>
       <c r="P112" t="n">
-        <v>-32.61</v>
+        <v>-33.32435503711559</v>
       </c>
       <c r="Q112" t="b">
         <v>0</v>
@@ -10396,19 +10484,19 @@
         <v>0</v>
       </c>
       <c r="T112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>falta familia</t>
+          <t>completo</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>p69-8617</t>
+          <t>p70-3658</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
@@ -10418,35 +10506,37 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>p69-8617</t>
+          <t>p70-3658</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="B113" t="n">
-        <v>3658</v>
+        <v>3654</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Achariaceae</t>
+          <t>Rubiaceae</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Lindackeria</t>
+          <t>Faramea</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>paludosa</t>
-        </is>
-      </c>
-      <c r="F113" t="n">
-        <v>3873</v>
+          <t>parvibractea</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>3876</t>
+        </is>
       </c>
       <c r="G113" t="n">
         <v>70</v>
@@ -10457,22 +10547,22 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="n">
-        <v>40.7185817747011</v>
+        <v>42.1253720851618</v>
       </c>
       <c r="L113" t="n">
-        <v>-31.5051012323677</v>
+        <v>-32.879883759186</v>
       </c>
       <c r="M113" t="n">
-        <v>0.022130638</v>
+        <v>0.02201823142746578</v>
       </c>
       <c r="N113" t="n">
-        <v>0.436691485</v>
+        <v>0.3956347601824302</v>
       </c>
       <c r="O113" t="n">
-        <v>2.122085858585857</v>
+        <v>1.86</v>
       </c>
       <c r="P113" t="n">
-        <v>-33.32435503711559</v>
+        <v>-33.86</v>
       </c>
       <c r="Q113" t="b">
         <v>0</v>
@@ -10496,7 +10586,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>p70-3658</t>
+          <t>p70-3654</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
@@ -10506,35 +10596,35 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>p70-3658</t>
+          <t>p70-3654</t>
         </is>
       </c>
       <c r="Z113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="B114" t="n">
-        <v>3658</v>
+        <v>3654</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Achariaceae</t>
+          <t>Rubiaceae</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Lindackeria</t>
+          <t>Faramea</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>paludosa</t>
+          <t>parvibractea</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>3873</v>
+        <v>3876</v>
       </c>
       <c r="G114" t="n">
         <v>70</v>
@@ -10542,27 +10632,25 @@
       <c r="H114" t="n">
         <v>2025</v>
       </c>
-      <c r="I114" t="n">
-        <v>3658</v>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="n">
-        <v>45.45</v>
+        <v>42.1253720851618</v>
       </c>
       <c r="L114" t="n">
-        <v>-32.26</v>
+        <v>-32.879883759186</v>
       </c>
       <c r="M114" t="n">
-        <v>0.022130638</v>
+        <v>0.02201823142746578</v>
       </c>
       <c r="N114" t="n">
-        <v>0.436691485</v>
+        <v>0.3956347601824302</v>
       </c>
       <c r="O114" t="n">
-        <v>2.122085858585857</v>
+        <v>1.86</v>
       </c>
       <c r="P114" t="n">
-        <v>-33.32435503711559</v>
+        <v>-33.86</v>
       </c>
       <c r="Q114" t="b">
         <v>0</v>
@@ -10586,7 +10674,7 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>p70-3658</t>
+          <t>p70-3654</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
@@ -10596,35 +10684,35 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>p70-3658</t>
+          <t>p70-3654</t>
         </is>
       </c>
       <c r="Z114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2205</v>
+        <v>2210</v>
       </c>
       <c r="B115" t="n">
-        <v>3654</v>
+        <v>3649</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
+          <t>Sapotaceae</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Faramea</t>
+          <t>Micropholis</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>parvibractea</t>
+          <t>guyanensis</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>3876</v>
+        <v>3878</v>
       </c>
       <c r="G115" t="n">
         <v>70</v>
@@ -10635,22 +10723,22 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="n">
-        <v>42.1253720851618</v>
+        <v>42.9613720358194</v>
       </c>
       <c r="L115" t="n">
-        <v>-32.879883759186</v>
+        <v>-28.8520520712957</v>
       </c>
       <c r="M115" t="n">
-        <v>0.02201823142746578</v>
+        <v>0.021352396</v>
       </c>
       <c r="N115" t="n">
-        <v>0.3956347601824302</v>
+        <v>0.483725522</v>
       </c>
       <c r="O115" t="n">
-        <v>1.86</v>
+        <v>2.737714646464645</v>
       </c>
       <c r="P115" t="n">
-        <v>-33.86</v>
+        <v>-31.18964284199364</v>
       </c>
       <c r="Q115" t="b">
         <v>0</v>
@@ -10674,7 +10762,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>p70-3654</t>
+          <t>p70-3649</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
@@ -10684,37 +10772,35 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>p70-3654</t>
+          <t>p70-3649</t>
         </is>
       </c>
       <c r="Z115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2205</v>
+        <v>2217</v>
       </c>
       <c r="B116" t="n">
-        <v>3654</v>
+        <v>3624</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
+          <t>Myristicaceae</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Faramea</t>
+          <t>Virola</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>parvibractea</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>3876</t>
-        </is>
+          <t>flexuosa</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>3881</v>
       </c>
       <c r="G116" t="n">
         <v>70</v>
@@ -10722,25 +10808,27 @@
       <c r="H116" t="n">
         <v>2025</v>
       </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="n">
+        <v>3624</v>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="n">
-        <v>42.1253720851618</v>
+        <v>52.95</v>
       </c>
       <c r="L116" t="n">
-        <v>-32.879883759186</v>
+        <v>-32.36</v>
       </c>
       <c r="M116" t="n">
-        <v>0.02201823142746578</v>
+        <v>0.02427045373167286</v>
       </c>
       <c r="N116" t="n">
-        <v>0.3956347601824302</v>
+        <v>0.4751152935178116</v>
       </c>
       <c r="O116" t="n">
-        <v>1.86</v>
+        <v>2.326243273844904</v>
       </c>
       <c r="P116" t="n">
-        <v>-33.86</v>
+        <v>-33.02171698766686</v>
       </c>
       <c r="Q116" t="b">
         <v>0</v>
@@ -10764,7 +10852,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>p70-3654</t>
+          <t>p70-3624</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
@@ -10772,37 +10860,33 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>p70-3654</t>
-        </is>
-      </c>
+      <c r="Y116" t="inlineStr"/>
       <c r="Z116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2210</v>
+        <v>2218</v>
       </c>
       <c r="B117" t="n">
-        <v>3649</v>
+        <v>3623</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sapotaceae</t>
+          <t>Melastomataceae</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Micropholis</t>
+          <t>Miconia</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>guyanensis</t>
+          <t>elata</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>3878</v>
+        <v>3882</v>
       </c>
       <c r="G117" t="n">
         <v>70</v>
@@ -10813,22 +10897,22 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="n">
-        <v>42.9613720358194</v>
+        <v>50.0511194882133</v>
       </c>
       <c r="L117" t="n">
-        <v>-28.8520520712957</v>
+        <v>-32.9644172724988</v>
       </c>
       <c r="M117" t="n">
-        <v>0.021352396</v>
+        <v>0.02344245815416083</v>
       </c>
       <c r="N117" t="n">
-        <v>0.483725522</v>
+        <v>0.4632356375118532</v>
       </c>
       <c r="O117" t="n">
-        <v>2.737714646464645</v>
+        <v>1.86</v>
       </c>
       <c r="P117" t="n">
-        <v>-31.18964284199364</v>
+        <v>-33.18</v>
       </c>
       <c r="Q117" t="b">
         <v>0</v>
@@ -10852,7 +10936,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>p70-3649</t>
+          <t>p70-3623</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
@@ -10862,35 +10946,35 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>p70-3649</t>
+          <t>p70-3623</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="B118" t="n">
-        <v>3624</v>
+        <v>3622</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Myristicaceae</t>
+          <t>Clusiaceae</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Virola</t>
+          <t>Chrysochlamys</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>flexuosa</t>
+          <t>membranacea</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>3881</v>
+        <v>3892</v>
       </c>
       <c r="G118" t="n">
         <v>70</v>
@@ -10898,27 +10982,25 @@
       <c r="H118" t="n">
         <v>2025</v>
       </c>
-      <c r="I118" t="n">
-        <v>3624</v>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="n">
-        <v>52.95</v>
+        <v>42.2106791938408</v>
       </c>
       <c r="L118" t="n">
-        <v>-32.36</v>
+        <v>-33.0984094704943</v>
       </c>
       <c r="M118" t="n">
-        <v>0.02427045373167286</v>
+        <v>0.01468680313508528</v>
       </c>
       <c r="N118" t="n">
-        <v>0.4751152935178116</v>
+        <v>0.4178782536686835</v>
       </c>
       <c r="O118" t="n">
-        <v>2.326243273844904</v>
+        <v>1.41</v>
       </c>
       <c r="P118" t="n">
-        <v>-33.02171698766686</v>
+        <v>-33.8</v>
       </c>
       <c r="Q118" t="b">
         <v>0</v>
@@ -10942,7 +11024,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>p70-3624</t>
+          <t>p70-3622</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
@@ -10950,33 +11032,37 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y118" t="inlineStr"/>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>p70-3622</t>
+        </is>
+      </c>
       <c r="Z118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2218</v>
+        <v>2224</v>
       </c>
       <c r="B119" t="n">
-        <v>3623</v>
+        <v>3629</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Melastomataceae</t>
+          <t>Meliaceae</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Miconia</t>
+          <t>Trichilia</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>elata</t>
+          <t>septentrionalis</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>3882</v>
+        <v>3885</v>
       </c>
       <c r="G119" t="n">
         <v>70</v>
@@ -10987,22 +11073,22 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="n">
-        <v>50.0511194882133</v>
+        <v>42.4863567490847</v>
       </c>
       <c r="L119" t="n">
-        <v>-32.9644172724988</v>
+        <v>-30.9830539249629</v>
       </c>
       <c r="M119" t="n">
-        <v>0.02344245815416083</v>
+        <v>0.03545007406100038</v>
       </c>
       <c r="N119" t="n">
-        <v>0.4632356375118532</v>
+        <v>0.4812524582095935</v>
       </c>
       <c r="O119" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="P119" t="n">
-        <v>-33.18</v>
+        <v>-32.25</v>
       </c>
       <c r="Q119" t="b">
         <v>0</v>
@@ -11026,7 +11112,7 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>p70-3623</t>
+          <t>p70-3629</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
@@ -11036,35 +11122,35 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>p70-3623</t>
+          <t>p70-3629</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2220</v>
+        <v>2233</v>
       </c>
       <c r="B120" t="n">
-        <v>3622</v>
+        <v>3642</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Clusiaceae</t>
+          <t>Rubiaceae</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Chrysochlamys</t>
+          <t>Chimarrhis</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>membranacea</t>
+          <t>cf glabriflora</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>3892</v>
+        <v>3897</v>
       </c>
       <c r="G120" t="n">
         <v>70</v>
@@ -11075,22 +11161,22 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="n">
-        <v>42.2106791938408</v>
+        <v>42.3110226596482</v>
       </c>
       <c r="L120" t="n">
-        <v>-33.0984094704943</v>
+        <v>-29.0136864851214</v>
       </c>
       <c r="M120" t="n">
-        <v>0.01468680313508528</v>
+        <v>0.01994461056810911</v>
       </c>
       <c r="N120" t="n">
-        <v>0.4178782536686835</v>
+        <v>0.4625106483743614</v>
       </c>
       <c r="O120" t="n">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="P120" t="n">
-        <v>-33.8</v>
+        <v>-31.42</v>
       </c>
       <c r="Q120" t="b">
         <v>0</v>
@@ -11114,7 +11200,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>p70-3622</t>
+          <t>p70-3642</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
@@ -11124,35 +11210,35 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>p70-3622</t>
+          <t>p70-3642</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2224</v>
+        <v>2238</v>
       </c>
       <c r="B121" t="n">
-        <v>3629</v>
+        <v>3635</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Meliaceae</t>
+          <t>Annonaceae</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Trichilia</t>
+          <t>Annona</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>septentrionalis</t>
+          <t>helosioides</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>3885</v>
+        <v>3889</v>
       </c>
       <c r="G121" t="n">
         <v>70</v>
@@ -11163,22 +11249,22 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="n">
-        <v>42.4863567490847</v>
+        <v>0.4147</v>
       </c>
       <c r="L121" t="n">
-        <v>-30.9830539249629</v>
+        <v>-33.34</v>
       </c>
       <c r="M121" t="n">
-        <v>0.03545007406100038</v>
+        <v>0.02329030068816614</v>
       </c>
       <c r="N121" t="n">
-        <v>0.4812524582095935</v>
+        <v>0.4286406242211068</v>
       </c>
       <c r="O121" t="n">
-        <v>1.94</v>
+        <v>0.67</v>
       </c>
       <c r="P121" t="n">
-        <v>-32.25</v>
+        <v>-34.74</v>
       </c>
       <c r="Q121" t="b">
         <v>0</v>
@@ -11202,7 +11288,7 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>p70-3629</t>
+          <t>p70-3635</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
@@ -11212,35 +11298,31 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>p70-3629</t>
+          <t>p70-3635</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2233</v>
+        <v>2239</v>
       </c>
       <c r="B122" t="n">
-        <v>3642</v>
+        <v>3643</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
+          <t>Melastomataceae</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Chimarrhis</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>cf glabriflora</t>
-        </is>
-      </c>
+          <t>Miconia</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="n">
-        <v>3897</v>
+        <v>3899</v>
       </c>
       <c r="G122" t="n">
         <v>70</v>
@@ -11248,25 +11330,27 @@
       <c r="H122" t="n">
         <v>2025</v>
       </c>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="n">
+        <v>3643</v>
+      </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="n">
-        <v>42.3110226596482</v>
+        <v>46.0901105921165</v>
       </c>
       <c r="L122" t="n">
-        <v>-29.0136864851214</v>
+        <v>-31.501955307122</v>
       </c>
       <c r="M122" t="n">
-        <v>0.01994461056810911</v>
+        <v>0.02072311918279543</v>
       </c>
       <c r="N122" t="n">
-        <v>0.4625106483743614</v>
+        <v>0.4566504070584768</v>
       </c>
       <c r="O122" t="n">
-        <v>1.91</v>
+        <v>2.193788836234638</v>
       </c>
       <c r="P122" t="n">
-        <v>-31.42</v>
+        <v>-33.15107748731418</v>
       </c>
       <c r="Q122" t="b">
         <v>0</v>
@@ -11281,7 +11365,7 @@
         <v>0</v>
       </c>
       <c r="U122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -11290,7 +11374,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>p70-3642</t>
+          <t>p70-3643</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
@@ -11298,19 +11382,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>p70-3642</t>
-        </is>
-      </c>
+      <c r="Y122" t="inlineStr"/>
       <c r="Z122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2238</v>
+        <v>2245</v>
       </c>
       <c r="B123" t="n">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -11319,16 +11399,16 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Annona</t>
+          <t>Guatteria</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>helosioides</t>
+          <t>cf multivenia</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>3889</v>
+        <v>3902</v>
       </c>
       <c r="G123" t="n">
         <v>70</v>
@@ -11339,22 +11419,22 @@
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="n">
-        <v>0.4147</v>
+        <v>42.6405238957477</v>
       </c>
       <c r="L123" t="n">
-        <v>-33.34</v>
+        <v>-33.9862141392051</v>
       </c>
       <c r="M123" t="n">
-        <v>0.02329030068816614</v>
+        <v>0.01173829239074074</v>
       </c>
       <c r="N123" t="n">
-        <v>0.4286406242211068</v>
+        <v>0.4273580210356233</v>
       </c>
       <c r="O123" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="P123" t="n">
-        <v>-34.74</v>
+        <v>-35.61</v>
       </c>
       <c r="Q123" t="b">
         <v>0</v>
@@ -11378,7 +11458,7 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>p70-3635</t>
+          <t>p70-3634</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
@@ -11388,31 +11468,35 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>p70-3635</t>
+          <t>p70-3634</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2239</v>
+        <v>2246</v>
       </c>
       <c r="B124" t="n">
-        <v>3643</v>
+        <v>3631</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Melastomataceae</t>
+          <t>Lauraceae</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Miconia</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
+          <t>Mespilodaphne</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>quixos</t>
+        </is>
+      </c>
       <c r="F124" t="n">
-        <v>3899</v>
+        <v>3903</v>
       </c>
       <c r="G124" t="n">
         <v>70</v>
@@ -11421,24 +11505,32 @@
         <v>2025</v>
       </c>
       <c r="I124" t="n">
-        <v>3643</v>
+        <v>3631</v>
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="n">
-        <v>46.0901105921165</v>
+        <v>43.77</v>
       </c>
       <c r="L124" t="n">
-        <v>-31.501955307122</v>
-      </c>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
+        <v>-31.43</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.01948619510337348</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4721467438734823</v>
+      </c>
+      <c r="O124" t="n">
+        <v>-0.02643156320996337</v>
+      </c>
+      <c r="P124" t="n">
+        <v>-33.88208264312594</v>
+      </c>
       <c r="Q124" t="b">
         <v>0</v>
       </c>
       <c r="R124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S124" t="b">
         <v>0</v>
@@ -11447,16 +11539,16 @@
         <v>0</v>
       </c>
       <c r="U124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>pesar bulk</t>
+          <t>completo</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>70-3643</t>
+          <t>p70-3631</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
@@ -11468,30 +11560,22 @@
       <c r="Z124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="n">
-        <v>2245</v>
-      </c>
+      <c r="A125" t="inlineStr"/>
       <c r="B125" t="n">
-        <v>3634</v>
+        <v>3645</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Annonaceae</t>
+          <t>Salicacia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Guatteria</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>cf multivenia</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>3902</v>
-      </c>
+          <t>Laetia</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
         <v>70</v>
       </c>
@@ -11501,28 +11585,20 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="n">
-        <v>42.6405238957477</v>
+        <v>42.6221781327326</v>
       </c>
       <c r="L125" t="n">
-        <v>-33.9862141392051</v>
-      </c>
-      <c r="M125" t="n">
-        <v>0.01173829239074074</v>
-      </c>
-      <c r="N125" t="n">
-        <v>0.4273580210356233</v>
-      </c>
-      <c r="O125" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="P125" t="n">
-        <v>-35.61</v>
-      </c>
+        <v>-33.053099414117</v>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
       <c r="Q125" t="b">
         <v>0</v>
       </c>
       <c r="R125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S125" t="b">
         <v>0</v>
@@ -11531,16 +11607,16 @@
         <v>0</v>
       </c>
       <c r="U125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>completo</t>
+          <t>pesar bulk</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>p70-3634</t>
+          <t>p70-3645</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
@@ -11548,71 +11624,45 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>p70-3634</t>
-        </is>
-      </c>
+      <c r="Y125" t="inlineStr"/>
       <c r="Z125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="n">
-        <v>2246</v>
-      </c>
+      <c r="A126" t="inlineStr"/>
       <c r="B126" t="n">
-        <v>3631</v>
+        <v>3650</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Mespilodaphne</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>quixos</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
-        <v>3903</v>
-      </c>
+          <t>indet</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
         <v>70</v>
       </c>
       <c r="H126" t="n">
         <v>2025</v>
       </c>
-      <c r="I126" t="n">
-        <v>3631</v>
-      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="n">
-        <v>43.77</v>
+        <v>42.13</v>
       </c>
       <c r="L126" t="n">
-        <v>-31.43</v>
-      </c>
-      <c r="M126" t="n">
-        <v>0.01948619510337348</v>
-      </c>
-      <c r="N126" t="n">
-        <v>0.4721467438734823</v>
-      </c>
-      <c r="O126" t="n">
-        <v>-0.02643156320996337</v>
-      </c>
-      <c r="P126" t="n">
-        <v>-33.88208264312594</v>
-      </c>
+        <v>-31.61</v>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
       <c r="Q126" t="b">
         <v>0</v>
       </c>
       <c r="R126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S126" t="b">
         <v>0</v>
@@ -11621,16 +11671,16 @@
         <v>0</v>
       </c>
       <c r="U126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>completo</t>
+          <t>pesar bulk</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>p70-3631</t>
+          <t>p70-3650</t>
         </is>
       </c>
       <c r="X126" t="inlineStr">
@@ -11642,24 +11692,28 @@
       <c r="Z126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="n">
+        <v>2288</v>
+      </c>
       <c r="B127" t="n">
-        <v>3645</v>
+        <v>8803</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Salicacia</t>
+          <t>Lecythidaceae</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Laetia</t>
+          <t>Eschweilera</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+      <c r="F127" t="n">
+        <v>3196</v>
+      </c>
       <c r="G127" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H127" t="n">
         <v>2025</v>
@@ -11667,20 +11721,28 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="n">
-        <v>42.6221781327326</v>
+        <v>42.0082033106923</v>
       </c>
       <c r="L127" t="n">
-        <v>-33.053099414117</v>
-      </c>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
+        <v>-31.0055258755093</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.013534934</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.4586319</v>
+      </c>
+      <c r="O127" t="n">
+        <v>2.284093434343433</v>
+      </c>
+      <c r="P127" t="n">
+        <v>-32.93247550371157</v>
+      </c>
       <c r="Q127" t="b">
         <v>0</v>
       </c>
       <c r="R127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S127" t="b">
         <v>0</v>
@@ -11693,12 +11755,12 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>pesar bulk</t>
+          <t>completo</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>p70-3645</t>
+          <t>p72-8803</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
@@ -11706,24 +11768,40 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y127" t="inlineStr"/>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>p72-8803</t>
+        </is>
+      </c>
       <c r="Z127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
+      <c r="A128" t="n">
+        <v>2289</v>
+      </c>
       <c r="B128" t="n">
-        <v>3650</v>
+        <v>8804</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>indet</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>Sapotaceae</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Pouteria</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>guianensis</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>3206</v>
+      </c>
       <c r="G128" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H128" t="n">
         <v>2025</v>
@@ -11731,20 +11809,28 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="n">
-        <v>42.13</v>
+        <v>44.1750069808239</v>
       </c>
       <c r="L128" t="n">
-        <v>-31.61</v>
-      </c>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
+        <v>-32.9490118438408</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.016758675</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.473760231</v>
+      </c>
+      <c r="O128" t="n">
+        <v>1.76566919191919</v>
+      </c>
+      <c r="P128" t="n">
+        <v>-34.8712479321315</v>
+      </c>
       <c r="Q128" t="b">
         <v>0</v>
       </c>
       <c r="R128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S128" t="b">
         <v>0</v>
@@ -11753,16 +11839,16 @@
         <v>0</v>
       </c>
       <c r="U128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>pesar bulk</t>
+          <t>completo</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>p70-3650</t>
+          <t>p72-8804</t>
         </is>
       </c>
       <c r="X128" t="inlineStr">
@@ -11770,44 +11856,66 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y128" t="inlineStr"/>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>p72-8804</t>
+        </is>
+      </c>
       <c r="Z128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>3643</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+      <c r="A129" t="n">
+        <v>2292</v>
+      </c>
+      <c r="B129" t="n">
+        <v>8811</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Moraceae</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Sorocea</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>steinbachii</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>3195</v>
+      </c>
       <c r="G129" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H129" t="n">
         <v>2025</v>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
+      <c r="K129" t="n">
+        <v>48.2294756543818</v>
+      </c>
+      <c r="L129" t="n">
+        <v>-29.5365889785962</v>
+      </c>
       <c r="M129" t="n">
-        <v>0.02072311918279543</v>
+        <v>0.021918119</v>
       </c>
       <c r="N129" t="n">
-        <v>0.4566504070584768</v>
+        <v>0.409271254</v>
       </c>
       <c r="O129" t="n">
-        <v>2.193788836234638</v>
+        <v>1.970878787878786</v>
       </c>
       <c r="P129" t="n">
-        <v>-33.15107748731418</v>
+        <v>-33.44810646871687</v>
       </c>
       <c r="Q129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R129" t="b">
         <v>0</v>
@@ -11816,19 +11924,19 @@
         <v>0</v>
       </c>
       <c r="T129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>pesar celulosa; falta familia</t>
+          <t>completo</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>p70-3643</t>
+          <t>p72-8811</t>
         </is>
       </c>
       <c r="X129" t="inlineStr">
@@ -11836,29 +11944,37 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>p72-8811</t>
+        </is>
+      </c>
       <c r="Z129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2288</v>
+        <v>2303</v>
       </c>
       <c r="B130" t="n">
-        <v>8803</v>
+        <v>8695</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Lecythidaceae</t>
+          <t>Rubiaceae</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Eschweilera</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>Pentagonia</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>amazonica</t>
+        </is>
+      </c>
       <c r="F130" t="n">
-        <v>3196</v>
+        <v>3214</v>
       </c>
       <c r="G130" t="n">
         <v>72</v>
@@ -11869,22 +11985,22 @@
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="n">
-        <v>42.0082033106923</v>
+        <v>42.8309647382475</v>
       </c>
       <c r="L130" t="n">
-        <v>-31.0055258755093</v>
+        <v>-31.9553391744547</v>
       </c>
       <c r="M130" t="n">
-        <v>0.013534934</v>
+        <v>0.019071872</v>
       </c>
       <c r="N130" t="n">
-        <v>0.4586319</v>
+        <v>0.460067295</v>
       </c>
       <c r="O130" t="n">
-        <v>2.284093434343433</v>
+        <v>2.867320707070705</v>
       </c>
       <c r="P130" t="n">
-        <v>-32.93247550371157</v>
+        <v>-33.52029480381761</v>
       </c>
       <c r="Q130" t="b">
         <v>0</v>
@@ -11899,7 +12015,7 @@
         <v>0</v>
       </c>
       <c r="U130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -11908,7 +12024,7 @@
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>p72-8803</t>
+          <t>p72-8695</t>
         </is>
       </c>
       <c r="X130" t="inlineStr">
@@ -11918,35 +12034,31 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>p72-8803</t>
+          <t>p72-8695</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2289</v>
+        <v>2309</v>
       </c>
       <c r="B131" t="n">
-        <v>8804</v>
+        <v>8690</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Sapotaceae</t>
+          <t>Myrtaceae</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Pouteria</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>guianensis</t>
-        </is>
-      </c>
+          <t>Eugenia</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="n">
-        <v>3206</v>
+        <v>3209</v>
       </c>
       <c r="G131" t="n">
         <v>72</v>
@@ -11957,22 +12069,22 @@
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="n">
-        <v>44.1750069808239</v>
+        <v>46.4981335324543</v>
       </c>
       <c r="L131" t="n">
-        <v>-32.9490118438408</v>
+        <v>-29.06502482523</v>
       </c>
       <c r="M131" t="n">
-        <v>0.016758675</v>
+        <v>0.039906421</v>
       </c>
       <c r="N131" t="n">
-        <v>0.473760231</v>
+        <v>0.432175376</v>
       </c>
       <c r="O131" t="n">
-        <v>1.76566919191919</v>
+        <v>2.370497474747473</v>
       </c>
       <c r="P131" t="n">
-        <v>-34.8712479321315</v>
+        <v>-29.56024899257688</v>
       </c>
       <c r="Q131" t="b">
         <v>0</v>
@@ -11987,7 +12099,7 @@
         <v>0</v>
       </c>
       <c r="U131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -11996,7 +12108,7 @@
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>p72-8804</t>
+          <t>p72-8690</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
@@ -12006,35 +12118,35 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>p72-8804</t>
+          <t>p72-8690</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2292</v>
+        <v>2310</v>
       </c>
       <c r="B132" t="n">
-        <v>8811</v>
+        <v>8689</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>Myristicaceae</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Sorocea</t>
+          <t>Virola</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>steinbachii</t>
+          <t>dixonii</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3195</v>
+        <v>3213</v>
       </c>
       <c r="G132" t="n">
         <v>72</v>
@@ -12045,22 +12157,22 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="n">
-        <v>48.2294756543818</v>
+        <v>45.5806811724309</v>
       </c>
       <c r="L132" t="n">
-        <v>-29.5365889785962</v>
+        <v>-31.5216615977631</v>
       </c>
       <c r="M132" t="n">
-        <v>0.021918119</v>
+        <v>0.015163699</v>
       </c>
       <c r="N132" t="n">
-        <v>0.409271254</v>
+        <v>0.468505884</v>
       </c>
       <c r="O132" t="n">
-        <v>1.970878787878786</v>
+        <v>2.74851515151515</v>
       </c>
       <c r="P132" t="n">
-        <v>-33.44810646871687</v>
+        <v>-32.67466002120891</v>
       </c>
       <c r="Q132" t="b">
         <v>0</v>
@@ -12084,7 +12196,7 @@
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>p72-8811</t>
+          <t>p72-8689</t>
         </is>
       </c>
       <c r="X132" t="inlineStr">
@@ -12094,35 +12206,35 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>p72-8811</t>
+          <t>p72-8689</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2303</v>
+        <v>2314</v>
       </c>
       <c r="B133" t="n">
-        <v>8695</v>
+        <v>8693</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
+          <t>Fabaceae</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Pentagonia</t>
+          <t>Inga</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>amazonica</t>
+          <t>multinervis</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3214</v>
+        <v>3198</v>
       </c>
       <c r="G133" t="n">
         <v>72</v>
@@ -12130,25 +12242,27 @@
       <c r="H133" t="n">
         <v>2025</v>
       </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="n">
+        <v>8693</v>
+      </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="n">
-        <v>42.8309647382475</v>
+        <v>47.23</v>
       </c>
       <c r="L133" t="n">
-        <v>-31.9553391744547</v>
+        <v>-32.18</v>
       </c>
       <c r="M133" t="n">
-        <v>0.019071872</v>
+        <v>0.02542784573637153</v>
       </c>
       <c r="N133" t="n">
-        <v>0.460067295</v>
+        <v>0.4667250763199911</v>
       </c>
       <c r="O133" t="n">
-        <v>2.867320707070705</v>
+        <v>-0.4411991989087207</v>
       </c>
       <c r="P133" t="n">
-        <v>-33.52029480381761</v>
+        <v>-33.82113297787679</v>
       </c>
       <c r="Q133" t="b">
         <v>0</v>
@@ -12172,7 +12286,7 @@
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>p72-8695</t>
+          <t>p72-8693</t>
         </is>
       </c>
       <c r="X133" t="inlineStr">
@@ -12180,33 +12294,33 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>p72-8695</t>
-        </is>
-      </c>
+      <c r="Y133" t="inlineStr"/>
       <c r="Z133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2309</v>
+        <v>2315</v>
       </c>
       <c r="B134" t="n">
-        <v>8690</v>
+        <v>8697</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Myrtaceae</t>
+          <t>Myristicaceae</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Eugenia</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>Otoba</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>parvifolia</t>
+        </is>
+      </c>
       <c r="F134" t="n">
-        <v>3209</v>
+        <v>3200</v>
       </c>
       <c r="G134" t="n">
         <v>72</v>
@@ -12217,22 +12331,22 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="n">
-        <v>46.4981335324543</v>
+        <v>42.7507551767448</v>
       </c>
       <c r="L134" t="n">
-        <v>-29.06502482523</v>
+        <v>-32.234447004374</v>
       </c>
       <c r="M134" t="n">
-        <v>0.039906421</v>
+        <v>0.01496271</v>
       </c>
       <c r="N134" t="n">
-        <v>0.432175376</v>
+        <v>0.480305405</v>
       </c>
       <c r="O134" t="n">
-        <v>2.370497474747473</v>
+        <v>1.290446969696968</v>
       </c>
       <c r="P134" t="n">
-        <v>-29.56024899257688</v>
+        <v>-30.84932640509014</v>
       </c>
       <c r="Q134" t="b">
         <v>0</v>
@@ -12247,7 +12361,7 @@
         <v>0</v>
       </c>
       <c r="U134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V134" t="inlineStr">
         <is>
@@ -12256,7 +12370,7 @@
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>p72-8690</t>
+          <t>p72-8697</t>
         </is>
       </c>
       <c r="X134" t="inlineStr">
@@ -12266,35 +12380,35 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>p72-8690</t>
+          <t>p72-8697</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2310</v>
+        <v>2319</v>
       </c>
       <c r="B135" t="n">
-        <v>8689</v>
+        <v>8699</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Myristicaceae</t>
+          <t>Rutaceae</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Virola</t>
+          <t>Amyris</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>dixonii</t>
+          <t>macrocarpa</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>3213</v>
+        <v>3197</v>
       </c>
       <c r="G135" t="n">
         <v>72</v>
@@ -12305,22 +12419,22 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="n">
-        <v>45.5806811724309</v>
+        <v>41.9002689842602</v>
       </c>
       <c r="L135" t="n">
-        <v>-31.5216615977631</v>
+        <v>-33.239736248638</v>
       </c>
       <c r="M135" t="n">
-        <v>0.015163699</v>
+        <v>0.019942396</v>
       </c>
       <c r="N135" t="n">
-        <v>0.468505884</v>
+        <v>0.460964682</v>
       </c>
       <c r="O135" t="n">
-        <v>2.74851515151515</v>
+        <v>1.160840909090907</v>
       </c>
       <c r="P135" t="n">
-        <v>-32.67466002120891</v>
+        <v>-34.56186935312832</v>
       </c>
       <c r="Q135" t="b">
         <v>0</v>
@@ -12344,7 +12458,7 @@
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>p72-8689</t>
+          <t>p72-8699</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
@@ -12354,63 +12468,57 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>p72-8689</t>
+          <t>p72-8699</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" t="n">
-        <v>2314</v>
-      </c>
+      <c r="A136" t="inlineStr"/>
       <c r="B136" t="n">
-        <v>8693</v>
+        <v>8688</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Fabaceae</t>
+          <t>Meliaceae</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Inga</t>
+          <t>Guarea</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>multinervis</t>
-        </is>
-      </c>
-      <c r="F136" t="n">
-        <v>3198</v>
-      </c>
+          <t>sp.</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="n">
         <v>72</v>
       </c>
       <c r="H136" t="n">
         <v>2025</v>
       </c>
-      <c r="I136" t="n">
-        <v>8693</v>
-      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="n">
-        <v>47.23</v>
+        <v>40.8654154955345</v>
       </c>
       <c r="L136" t="n">
-        <v>-32.18</v>
+        <v>-28.7781098108072</v>
       </c>
       <c r="M136" t="n">
-        <v>0.02542784573637153</v>
+        <v>0.026106295</v>
       </c>
       <c r="N136" t="n">
-        <v>0.4667250763199911</v>
+        <v>0.456459654</v>
       </c>
       <c r="O136" t="n">
-        <v>-0.4411991989087207</v>
+        <v>2.867320707070705</v>
       </c>
       <c r="P136" t="n">
-        <v>-33.82113297787679</v>
+        <v>-30.49869734888653</v>
       </c>
       <c r="Q136" t="b">
         <v>0</v>
@@ -12434,7 +12542,7 @@
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>p72-8693</t>
+          <t>p72-8688</t>
         </is>
       </c>
       <c r="X136" t="inlineStr">
@@ -12442,36 +12550,40 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y136" t="inlineStr"/>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>p72-8688</t>
+        </is>
+      </c>
       <c r="Z136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2315</v>
+        <v>2368</v>
       </c>
       <c r="B137" t="n">
-        <v>8697</v>
+        <v>8849</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Myristicaceae</t>
+          <t>Calophyllaceae</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Otoba</t>
+          <t>Marila</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>parvifolia</t>
+          <t>grandiflora</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>3200</v>
+        <v>3163</v>
       </c>
       <c r="G137" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H137" t="n">
         <v>2025</v>
@@ -12479,22 +12591,22 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="n">
-        <v>42.7507551767448</v>
+        <v>42.584605794486</v>
       </c>
       <c r="L137" t="n">
-        <v>-32.234447004374</v>
+        <v>-31.2207105692877</v>
       </c>
       <c r="M137" t="n">
-        <v>0.01496271</v>
+        <v>0.0157979699642389</v>
       </c>
       <c r="N137" t="n">
-        <v>0.480305405</v>
+        <v>0.4892875807439671</v>
       </c>
       <c r="O137" t="n">
-        <v>1.290446969696968</v>
+        <v>0.44</v>
       </c>
       <c r="P137" t="n">
-        <v>-30.84932640509014</v>
+        <v>-33.24</v>
       </c>
       <c r="Q137" t="b">
         <v>0</v>
@@ -12518,7 +12630,7 @@
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>p72-8697</t>
+          <t>p74-8849</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
@@ -12528,38 +12640,34 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>p72-8697</t>
+          <t>p74-8849</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2319</v>
+        <v>2374</v>
       </c>
       <c r="B138" t="n">
-        <v>8699</v>
+        <v>8853</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Rutaceae</t>
+          <t>Myrtaceae</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Amyris</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>macrocarpa</t>
-        </is>
-      </c>
+          <t>Eugenia</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="n">
-        <v>3197</v>
+        <v>3266</v>
       </c>
       <c r="G138" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H138" t="n">
         <v>2025</v>
@@ -12567,22 +12675,22 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="n">
-        <v>41.9002689842602</v>
+        <v>43.9837046243642</v>
       </c>
       <c r="L138" t="n">
-        <v>-33.239736248638</v>
+        <v>-33.1595942086546</v>
       </c>
       <c r="M138" t="n">
-        <v>0.019942396</v>
+        <v>0.01315526705850149</v>
       </c>
       <c r="N138" t="n">
-        <v>0.460964682</v>
+        <v>0.4473774700942126</v>
       </c>
       <c r="O138" t="n">
-        <v>1.160840909090907</v>
+        <v>-0.42</v>
       </c>
       <c r="P138" t="n">
-        <v>-34.56186935312832</v>
+        <v>-34.64</v>
       </c>
       <c r="Q138" t="b">
         <v>0</v>
@@ -12597,7 +12705,7 @@
         <v>0</v>
       </c>
       <c r="U138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V138" t="inlineStr">
         <is>
@@ -12606,7 +12714,7 @@
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>p72-8699</t>
+          <t>p74-8853</t>
         </is>
       </c>
       <c r="X138" t="inlineStr">
@@ -12616,34 +12724,38 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>p72-8699</t>
+          <t>p74-8853</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
+      <c r="A139" t="n">
+        <v>2375</v>
+      </c>
       <c r="B139" t="n">
-        <v>8688</v>
+        <v>8854</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Meliaceae</t>
+          <t>Moraceae</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Guarea</t>
+          <t>Sorocea</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>sp.</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
+          <t>pubivena</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>3268</v>
+      </c>
       <c r="G139" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H139" t="n">
         <v>2025</v>
@@ -12651,22 +12763,22 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="n">
-        <v>40.8654154955345</v>
+        <v>41.94733475458</v>
       </c>
       <c r="L139" t="n">
-        <v>-28.7781098108072</v>
+        <v>-29.5062469126404</v>
       </c>
       <c r="M139" t="n">
-        <v>0.026106295</v>
+        <v>0.02065846271337194</v>
       </c>
       <c r="N139" t="n">
-        <v>0.456459654</v>
+        <v>0.3932217774359631</v>
       </c>
       <c r="O139" t="n">
-        <v>2.867320707070705</v>
+        <v>-0.3</v>
       </c>
       <c r="P139" t="n">
-        <v>-30.49869734888653</v>
+        <v>-31.32</v>
       </c>
       <c r="Q139" t="b">
         <v>0</v>
@@ -12690,7 +12802,7 @@
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>p72-8688</t>
+          <t>p74-8854</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
@@ -12700,46 +12812,64 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>p72-8688</t>
+          <t>p74-8854</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>8893</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
+      <c r="A140" t="n">
+        <v>2376</v>
+      </c>
+      <c r="B140" t="n">
+        <v>8855</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Annonaceae</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Guatteria</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>same as 3262</t>
+        </is>
+      </c>
       <c r="G140" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H140" t="n">
         <v>2025</v>
       </c>
-      <c r="I140" t="inlineStr"/>
+      <c r="I140" t="n">
+        <v>8855</v>
+      </c>
       <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
+      <c r="K140" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="L140" t="n">
+        <v>-32.69</v>
+      </c>
       <c r="M140" t="n">
-        <v>0.0140003582445462</v>
+        <v>0.01267796706827776</v>
       </c>
       <c r="N140" t="n">
-        <v>0.3883734423353893</v>
+        <v>0.4200181121551486</v>
       </c>
       <c r="O140" t="n">
-        <v>0.8692445291019997</v>
+        <v>0.4521413591416198</v>
       </c>
       <c r="P140" t="n">
-        <v>-35.5916730458568</v>
+        <v>-34.28859239299114</v>
       </c>
       <c r="Q140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R140" t="b">
         <v>0</v>
@@ -12748,19 +12878,19 @@
         <v>0</v>
       </c>
       <c r="T140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U140" t="b">
         <v>1</v>
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>pesar celulosa; falta familia</t>
+          <t>completo</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>p72-8893</t>
+          <t>p74-8855</t>
         </is>
       </c>
       <c r="X140" t="inlineStr">
@@ -12773,28 +12903,24 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2368</v>
+        <v>2380</v>
       </c>
       <c r="B141" t="n">
-        <v>8849</v>
+        <v>8863</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Calophyllaceae</t>
+          <t>Lauraceae</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Marila</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>grandiflora</t>
-        </is>
-      </c>
+          <t>Pleurothyrium</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="n">
-        <v>3163</v>
+        <v>3273</v>
       </c>
       <c r="G141" t="n">
         <v>74</v>
@@ -12805,22 +12931,22 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="n">
-        <v>42.584605794486</v>
+        <v>39.9182128244988</v>
       </c>
       <c r="L141" t="n">
-        <v>-31.2207105692877</v>
+        <v>-30.9506111161297</v>
       </c>
       <c r="M141" t="n">
-        <v>0.0157979699642389</v>
+        <v>0.01887504041753914</v>
       </c>
       <c r="N141" t="n">
-        <v>0.4892875807439671</v>
+        <v>0.4521728216082592</v>
       </c>
       <c r="O141" t="n">
-        <v>0.44</v>
+        <v>-0.82</v>
       </c>
       <c r="P141" t="n">
-        <v>-33.24</v>
+        <v>-34.43</v>
       </c>
       <c r="Q141" t="b">
         <v>0</v>
@@ -12835,7 +12961,7 @@
         <v>0</v>
       </c>
       <c r="U141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V141" t="inlineStr">
         <is>
@@ -12844,7 +12970,7 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>p74-8849</t>
+          <t>p74-8863</t>
         </is>
       </c>
       <c r="X141" t="inlineStr">
@@ -12854,31 +12980,31 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>p74-8849</t>
+          <t>p74-8863</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2374</v>
+        <v>2380</v>
       </c>
       <c r="B142" t="n">
-        <v>8853</v>
+        <v>8863</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Myrtaceae</t>
+          <t>Lauraceae</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Eugenia</t>
+          <t>Pleurothyrium</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="n">
-        <v>3266</v>
+        <v>3273</v>
       </c>
       <c r="G142" t="n">
         <v>74</v>
@@ -12889,22 +13015,22 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="n">
-        <v>43.9837046243642</v>
+        <v>0.4445</v>
       </c>
       <c r="L142" t="n">
-        <v>-33.1595942086546</v>
+        <v>-31.32</v>
       </c>
       <c r="M142" t="n">
-        <v>0.01315526705850149</v>
+        <v>0.01887504041753914</v>
       </c>
       <c r="N142" t="n">
-        <v>0.4473774700942126</v>
+        <v>0.4521728216082592</v>
       </c>
       <c r="O142" t="n">
-        <v>-0.42</v>
+        <v>-0.82</v>
       </c>
       <c r="P142" t="n">
-        <v>-34.64</v>
+        <v>-34.43</v>
       </c>
       <c r="Q142" t="b">
         <v>0</v>
@@ -12928,7 +13054,7 @@
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>p74-8853</t>
+          <t>p74-8863</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
@@ -12938,17 +13064,17 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>p74-8853</t>
+          <t>p74-8863</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2375</v>
+        <v>2382</v>
       </c>
       <c r="B143" t="n">
-        <v>8854</v>
+        <v>8859</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -12957,16 +13083,16 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Sorocea</t>
+          <t>Pseudolmedia</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>pubivena</t>
+          <t>laevigata</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>3268</v>
+        <v>3264</v>
       </c>
       <c r="G143" t="n">
         <v>74</v>
@@ -12977,22 +13103,22 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="n">
-        <v>41.94733475458</v>
+        <v>42.1040303643344</v>
       </c>
       <c r="L143" t="n">
-        <v>-29.5062469126404</v>
+        <v>-33.2155181816902</v>
       </c>
       <c r="M143" t="n">
-        <v>0.02065846271337194</v>
+        <v>0.01519611827639625</v>
       </c>
       <c r="N143" t="n">
-        <v>0.3932217774359631</v>
+        <v>0.3990582769402648</v>
       </c>
       <c r="O143" t="n">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
       <c r="P143" t="n">
-        <v>-31.32</v>
+        <v>-34.77</v>
       </c>
       <c r="Q143" t="b">
         <v>0</v>
@@ -13016,7 +13142,7 @@
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>p74-8854</t>
+          <t>p74-8859</t>
         </is>
       </c>
       <c r="X143" t="inlineStr">
@@ -13026,32 +13152,36 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>p74-8854</t>
+          <t>p74-8859</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2376</v>
+        <v>2388</v>
       </c>
       <c r="B144" t="n">
-        <v>8855</v>
+        <v>8838</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Annonaceae</t>
+          <t>Sapotaceae</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Guatteria</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
+          <t>Pouteria</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>cuspidata</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>same as 3262</t>
+          <t>same as 3244</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -13060,27 +13190,25 @@
       <c r="H144" t="n">
         <v>2025</v>
       </c>
-      <c r="I144" t="n">
-        <v>8855</v>
-      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="n">
-        <v>44.84</v>
+        <v>45.6563961631267</v>
       </c>
       <c r="L144" t="n">
-        <v>-32.69</v>
+        <v>-31.408251888962</v>
       </c>
       <c r="M144" t="n">
-        <v>0.01267796706827776</v>
+        <v>0.01506027773689399</v>
       </c>
       <c r="N144" t="n">
-        <v>0.4200181121551486</v>
+        <v>0.4810743319827603</v>
       </c>
       <c r="O144" t="n">
-        <v>0.4521413591416198</v>
+        <v>0.25</v>
       </c>
       <c r="P144" t="n">
-        <v>-34.28859239299114</v>
+        <v>-33.65</v>
       </c>
       <c r="Q144" t="b">
         <v>0</v>
@@ -13095,7 +13223,7 @@
         <v>0</v>
       </c>
       <c r="U144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V144" t="inlineStr">
         <is>
@@ -13104,7 +13232,7 @@
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>p74-8855</t>
+          <t>p74-8838</t>
         </is>
       </c>
       <c r="X144" t="inlineStr">
@@ -13112,29 +13240,37 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y144" t="inlineStr"/>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>p74-8838</t>
+        </is>
+      </c>
       <c r="Z144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2380</v>
+        <v>2389</v>
       </c>
       <c r="B145" t="n">
-        <v>8863</v>
+        <v>8840</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
+          <t>Sapotaceae</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Pleurothyrium</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
+          <t>Pouteria</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>megaphylla</t>
+        </is>
+      </c>
       <c r="F145" t="n">
-        <v>3273</v>
+        <v>3269</v>
       </c>
       <c r="G145" t="n">
         <v>74</v>
@@ -13145,22 +13281,22 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="n">
-        <v>39.9182128244988</v>
+        <v>44.5740328512561</v>
       </c>
       <c r="L145" t="n">
-        <v>-30.9506111161297</v>
+        <v>-33.5302479904779</v>
       </c>
       <c r="M145" t="n">
-        <v>0.01887504041753914</v>
+        <v>0.013054872322637</v>
       </c>
       <c r="N145" t="n">
-        <v>0.4521728216082592</v>
+        <v>0.4551252723799056</v>
       </c>
       <c r="O145" t="n">
-        <v>-0.82</v>
+        <v>-1.16</v>
       </c>
       <c r="P145" t="n">
-        <v>-34.43</v>
+        <v>-34.88</v>
       </c>
       <c r="Q145" t="b">
         <v>0</v>
@@ -13175,7 +13311,7 @@
         <v>0</v>
       </c>
       <c r="U145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -13184,7 +13320,7 @@
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>p74-8863</t>
+          <t>p74-8840</t>
         </is>
       </c>
       <c r="X145" t="inlineStr">
@@ -13194,31 +13330,35 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>p74-8863</t>
+          <t>p74-8840</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2380</v>
+        <v>2390</v>
       </c>
       <c r="B146" t="n">
-        <v>8863</v>
+        <v>8839</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
+          <t>Salicaceae</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Pleurothyrium</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
+          <t>Tetrathylacium</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>macrophyllum</t>
+        </is>
+      </c>
       <c r="F146" t="n">
-        <v>3273</v>
+        <v>3280</v>
       </c>
       <c r="G146" t="n">
         <v>74</v>
@@ -13226,25 +13366,27 @@
       <c r="H146" t="n">
         <v>2025</v>
       </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="n">
+        <v>8839</v>
+      </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="n">
-        <v>0.4445</v>
+        <v>47.43</v>
       </c>
       <c r="L146" t="n">
-        <v>-31.32</v>
+        <v>-33.56</v>
       </c>
       <c r="M146" t="n">
-        <v>0.01887504041753914</v>
+        <v>0.02064776750558031</v>
       </c>
       <c r="N146" t="n">
-        <v>0.4521728216082592</v>
+        <v>0.4192067594363539</v>
       </c>
       <c r="O146" t="n">
-        <v>-0.82</v>
+        <v>-1.097854219839444</v>
       </c>
       <c r="P146" t="n">
-        <v>-34.43</v>
+        <v>-34.66376741181293</v>
       </c>
       <c r="Q146" t="b">
         <v>0</v>
@@ -13259,7 +13401,7 @@
         <v>0</v>
       </c>
       <c r="U146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -13268,7 +13410,7 @@
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>p74-8863</t>
+          <t>p74-8839</t>
         </is>
       </c>
       <c r="X146" t="inlineStr">
@@ -13276,37 +13418,33 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>p74-8863</t>
-        </is>
-      </c>
+      <c r="Y146" t="inlineStr"/>
       <c r="Z146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2382</v>
+        <v>2393</v>
       </c>
       <c r="B147" t="n">
-        <v>8859</v>
+        <v>8832</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>Violaceae</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Pseudolmedia</t>
+          <t>Leonia</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>laevigata</t>
+          <t>longifolium</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>3264</v>
+        <v>3270</v>
       </c>
       <c r="G147" t="n">
         <v>74</v>
@@ -13317,28 +13455,20 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="n">
-        <v>42.1040303643344</v>
+        <v>40.509559197114</v>
       </c>
       <c r="L147" t="n">
-        <v>-33.2155181816902</v>
-      </c>
-      <c r="M147" t="n">
-        <v>0.01519611827639625</v>
-      </c>
-      <c r="N147" t="n">
-        <v>0.3990582769402648</v>
-      </c>
-      <c r="O147" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P147" t="n">
-        <v>-34.77</v>
-      </c>
+        <v>-32.1358652529169</v>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
       <c r="Q147" t="b">
         <v>0</v>
       </c>
       <c r="R147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S147" t="b">
         <v>0</v>
@@ -13351,12 +13481,12 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>completo</t>
+          <t>pesar bulk</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>p74-8859</t>
+          <t>p74-8832</t>
         </is>
       </c>
       <c r="X147" t="inlineStr">
@@ -13364,19 +13494,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>p74-8859</t>
-        </is>
-      </c>
+      <c r="Y147" t="inlineStr"/>
       <c r="Z147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2388</v>
+        <v>2398</v>
       </c>
       <c r="B148" t="n">
-        <v>8838</v>
+        <v>8829</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -13390,39 +13516,37 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>cuspidata</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>same as 3244</t>
-        </is>
-      </c>
+          <t>vernicosa</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
         <v>74</v>
       </c>
       <c r="H148" t="n">
         <v>2025</v>
       </c>
-      <c r="I148" t="inlineStr"/>
+      <c r="I148" t="n">
+        <v>8829</v>
+      </c>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="n">
-        <v>45.6563961631267</v>
+        <v>49.45</v>
       </c>
       <c r="L148" t="n">
-        <v>-31.408251888962</v>
+        <v>-32.67</v>
       </c>
       <c r="M148" t="n">
-        <v>0.01506027773689399</v>
+        <v>0.01478326609717292</v>
       </c>
       <c r="N148" t="n">
-        <v>0.4810743319827603</v>
+        <v>0.4472376407343944</v>
       </c>
       <c r="O148" t="n">
-        <v>0.25</v>
+        <v>1.278813389479717</v>
       </c>
       <c r="P148" t="n">
-        <v>-33.65</v>
+        <v>-34.79099254006313</v>
       </c>
       <c r="Q148" t="b">
         <v>0</v>
@@ -13446,7 +13570,7 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>p74-8838</t>
+          <t>p74-8829</t>
         </is>
       </c>
       <c r="X148" t="inlineStr">
@@ -13454,37 +13578,33 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>p74-8838</t>
-        </is>
-      </c>
+      <c r="Y148" t="inlineStr"/>
       <c r="Z148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2389</v>
+        <v>2399</v>
       </c>
       <c r="B149" t="n">
-        <v>8840</v>
+        <v>8830</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Sapotaceae</t>
+          <t>Moraceae</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Pouteria</t>
+          <t>Pseudolmedia</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>megaphylla</t>
+          <t>laevis</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>3269</v>
+        <v>3265</v>
       </c>
       <c r="G149" t="n">
         <v>74</v>
@@ -13492,25 +13612,27 @@
       <c r="H149" t="n">
         <v>2025</v>
       </c>
-      <c r="I149" t="inlineStr"/>
+      <c r="I149" t="n">
+        <v>8830</v>
+      </c>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="n">
-        <v>44.5740328512561</v>
+        <v>45.35</v>
       </c>
       <c r="L149" t="n">
-        <v>-33.5302479904779</v>
+        <v>-30.61</v>
       </c>
       <c r="M149" t="n">
-        <v>0.013054872322637</v>
+        <v>0.01604169277097844</v>
       </c>
       <c r="N149" t="n">
-        <v>0.4551252723799056</v>
+        <v>0.4064424404546074</v>
       </c>
       <c r="O149" t="n">
-        <v>-1.16</v>
+        <v>1.184250654591758</v>
       </c>
       <c r="P149" t="n">
-        <v>-34.88</v>
+        <v>-32.35057997101688</v>
       </c>
       <c r="Q149" t="b">
         <v>0</v>
@@ -13534,7 +13656,7 @@
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>p74-8840</t>
+          <t>p74-8830</t>
         </is>
       </c>
       <c r="X149" t="inlineStr">
@@ -13542,344 +13664,8 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>p74-8840</t>
-        </is>
-      </c>
+      <c r="Y149" t="inlineStr"/>
       <c r="Z149" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>2390</v>
-      </c>
-      <c r="B150" t="n">
-        <v>8839</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Salicaceae</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Tetrathylacium</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>macrophyllum</t>
-        </is>
-      </c>
-      <c r="F150" t="n">
-        <v>3280</v>
-      </c>
-      <c r="G150" t="n">
-        <v>74</v>
-      </c>
-      <c r="H150" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I150" t="n">
-        <v>8839</v>
-      </c>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="n">
-        <v>47.43</v>
-      </c>
-      <c r="L150" t="n">
-        <v>-33.56</v>
-      </c>
-      <c r="M150" t="n">
-        <v>0.02064776750558031</v>
-      </c>
-      <c r="N150" t="n">
-        <v>0.4192067594363539</v>
-      </c>
-      <c r="O150" t="n">
-        <v>-1.097854219839444</v>
-      </c>
-      <c r="P150" t="n">
-        <v>-34.66376741181293</v>
-      </c>
-      <c r="Q150" t="b">
-        <v>0</v>
-      </c>
-      <c r="R150" t="b">
-        <v>0</v>
-      </c>
-      <c r="S150" t="b">
-        <v>0</v>
-      </c>
-      <c r="T150" t="b">
-        <v>0</v>
-      </c>
-      <c r="U150" t="b">
-        <v>0</v>
-      </c>
-      <c r="V150" t="inlineStr">
-        <is>
-          <t>completo</t>
-        </is>
-      </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>p74-8839</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr"/>
-      <c r="Z150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>2393</v>
-      </c>
-      <c r="B151" t="n">
-        <v>8832</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Violaceae</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Leonia</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>longifolium</t>
-        </is>
-      </c>
-      <c r="F151" t="n">
-        <v>3270</v>
-      </c>
-      <c r="G151" t="n">
-        <v>74</v>
-      </c>
-      <c r="H151" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="n">
-        <v>40.509559197114</v>
-      </c>
-      <c r="L151" t="n">
-        <v>-32.1358652529169</v>
-      </c>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="b">
-        <v>0</v>
-      </c>
-      <c r="R151" t="b">
-        <v>1</v>
-      </c>
-      <c r="S151" t="b">
-        <v>0</v>
-      </c>
-      <c r="T151" t="b">
-        <v>0</v>
-      </c>
-      <c r="U151" t="b">
-        <v>0</v>
-      </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>pesar bulk</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>p74-8832</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr"/>
-      <c r="Z151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>2398</v>
-      </c>
-      <c r="B152" t="n">
-        <v>8829</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Sapotaceae</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Pouteria</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>vernicosa</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="n">
-        <v>74</v>
-      </c>
-      <c r="H152" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I152" t="n">
-        <v>8829</v>
-      </c>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="n">
-        <v>49.45</v>
-      </c>
-      <c r="L152" t="n">
-        <v>-32.67</v>
-      </c>
-      <c r="M152" t="n">
-        <v>0.01478326609717292</v>
-      </c>
-      <c r="N152" t="n">
-        <v>0.4472376407343944</v>
-      </c>
-      <c r="O152" t="n">
-        <v>1.278813389479717</v>
-      </c>
-      <c r="P152" t="n">
-        <v>-34.79099254006313</v>
-      </c>
-      <c r="Q152" t="b">
-        <v>0</v>
-      </c>
-      <c r="R152" t="b">
-        <v>0</v>
-      </c>
-      <c r="S152" t="b">
-        <v>0</v>
-      </c>
-      <c r="T152" t="b">
-        <v>0</v>
-      </c>
-      <c r="U152" t="b">
-        <v>0</v>
-      </c>
-      <c r="V152" t="inlineStr">
-        <is>
-          <t>completo</t>
-        </is>
-      </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>p74-8829</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
-      <c r="Y152" t="inlineStr"/>
-      <c r="Z152" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>2399</v>
-      </c>
-      <c r="B153" t="n">
-        <v>8830</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Moraceae</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Pseudolmedia</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>laevis</t>
-        </is>
-      </c>
-      <c r="F153" t="n">
-        <v>3265</v>
-      </c>
-      <c r="G153" t="n">
-        <v>74</v>
-      </c>
-      <c r="H153" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I153" t="n">
-        <v>8830</v>
-      </c>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="n">
-        <v>45.35</v>
-      </c>
-      <c r="L153" t="n">
-        <v>-30.61</v>
-      </c>
-      <c r="M153" t="n">
-        <v>0.01604169277097844</v>
-      </c>
-      <c r="N153" t="n">
-        <v>0.4064424404546074</v>
-      </c>
-      <c r="O153" t="n">
-        <v>1.184250654591758</v>
-      </c>
-      <c r="P153" t="n">
-        <v>-32.35057997101688</v>
-      </c>
-      <c r="Q153" t="b">
-        <v>0</v>
-      </c>
-      <c r="R153" t="b">
-        <v>0</v>
-      </c>
-      <c r="S153" t="b">
-        <v>0</v>
-      </c>
-      <c r="T153" t="b">
-        <v>0</v>
-      </c>
-      <c r="U153" t="b">
-        <v>0</v>
-      </c>
-      <c r="V153" t="inlineStr">
-        <is>
-          <t>completo</t>
-        </is>
-      </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>p74-8830</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr"/>
-      <c r="Z153" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13892,7 +13678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z40"/>
+  <dimension ref="A1:Z32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15487,10 +15273,10 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>52.1703514062085</v>
+        <v>0.4488</v>
       </c>
       <c r="L19" t="n">
-        <v>-31.974735763936</v>
+        <v>-30.83</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -15573,10 +15359,10 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.4488</v>
+        <v>52.1703514062085</v>
       </c>
       <c r="L20" t="n">
-        <v>-30.83</v>
+        <v>-31.974735763936</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -16127,29 +15913,29 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2141</v>
+        <v>2154</v>
       </c>
       <c r="B27" t="n">
-        <v>8869</v>
+        <v>8885</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sapotaceae</t>
+          <t>Apocynaceae</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sarcaulus</t>
+          <t>Aspidosperma</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>aff. oblatus</t>
+          <t>aff. excelsum</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -16158,25 +15944,27 @@
       <c r="H27" t="n">
         <v>2025</v>
       </c>
-      <c r="I27" t="n">
-        <v>8869</v>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
-        <v>44.54</v>
-      </c>
-      <c r="L27" t="n">
-        <v>-29.77</v>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>0.015294916</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.488282508</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.8692272727272705</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-33.91217433722163</v>
+      </c>
       <c r="Q27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="b">
         <v>0</v>
@@ -16189,12 +15977,12 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>pesar bulk</t>
+          <t>pesar celulosa</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>68-8869</t>
+          <t>p68-8885</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -16202,81 +15990,65 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>p68-8885</t>
+        </is>
+      </c>
       <c r="Z27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>2154</v>
-      </c>
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>8885</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Apocynaceae</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Aspidosperma</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>aff. excelsum</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>3921</t>
-        </is>
-      </c>
+        <v>8640</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
         <v>68</v>
       </c>
       <c r="H28" t="n">
         <v>2025</v>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>8640</v>
+      </c>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="n">
-        <v>0.015294916</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.488282508</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0.8692272727272705</v>
-      </c>
-      <c r="P28" t="n">
-        <v>-33.91217433722163</v>
-      </c>
+      <c r="K28" t="n">
+        <v>44.8257164326167</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-27.3770370113265</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="b">
+        <v>0</v>
+      </c>
+      <c r="R28" t="b">
         <v>1</v>
       </c>
-      <c r="R28" t="b">
-        <v>0</v>
-      </c>
       <c r="S28" t="b">
         <v>0</v>
       </c>
       <c r="T28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>pesar celulosa</t>
+          <t>pesar bulk; falta familia</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>p68-8885</t>
+          <t>p68-8640</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -16284,17 +16056,13 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>p68-8885</t>
-        </is>
-      </c>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>8640</v>
+        <v>8865</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -16307,24 +16075,32 @@
         <v>2025</v>
       </c>
       <c r="I29" t="n">
-        <v>8640</v>
+        <v>9865</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
-        <v>44.8257164326167</v>
+        <v>50.7386705764376</v>
       </c>
       <c r="L29" t="n">
-        <v>-27.3770370113265</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+        <v>-32.9258451761764</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.02234992814914083</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.4489033340843991</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.108676665915091</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-33.46661356502295</v>
+      </c>
       <c r="Q29" t="b">
         <v>0</v>
       </c>
       <c r="R29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="b">
         <v>0</v>
@@ -16337,12 +16113,12 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>pesar bulk; falta familia</t>
+          <t>falta familia</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>p68-8640</t>
+          <t>p68-8865</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -16356,27 +16132,33 @@
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>9865</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+        <v>3645</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Salicacia</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Laetia</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H30" t="n">
         <v>2025</v>
       </c>
-      <c r="I30" t="n">
-        <v>9865</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
-        <v>50.7386705764376</v>
+        <v>42.6221781327326</v>
       </c>
       <c r="L30" t="n">
-        <v>-32.9258451761764</v>
+        <v>-33.053099414117</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -16392,19 +16174,19 @@
         <v>0</v>
       </c>
       <c r="T30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="b">
         <v>1</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>pesar bulk; falta familia</t>
+          <t>pesar bulk</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>68-9865</t>
+          <t>p70-3645</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -16417,60 +16199,58 @@
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>8865</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>3650</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>indet</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H31" t="n">
         <v>2025</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
-        <v>0.02234992814914083</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.4489033340843991</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.108676665915091</v>
-      </c>
-      <c r="P31" t="n">
-        <v>-33.46661356502295</v>
-      </c>
+      <c r="K31" t="n">
+        <v>42.13</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-31.61</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="b">
+        <v>0</v>
+      </c>
+      <c r="R31" t="b">
         <v>1</v>
       </c>
-      <c r="R31" t="b">
-        <v>0</v>
-      </c>
       <c r="S31" t="b">
         <v>0</v>
       </c>
       <c r="T31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U31" t="b">
         <v>1</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>pesar celulosa; falta familia</t>
+          <t>pesar bulk</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>p68-8865</t>
+          <t>p70-3650</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -16482,61 +16262,71 @@
       <c r="Z31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>8869</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="A32" t="n">
+        <v>2393</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8832</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Violaceae</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Leonia</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>longifolium</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>3270</v>
+      </c>
       <c r="G32" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H32" t="n">
         <v>2025</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="n">
-        <v>0.01245650406992576</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.4623296600125005</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.2163299630070622</v>
-      </c>
-      <c r="P32" t="n">
-        <v>-32.72903641196186</v>
-      </c>
+      <c r="K32" t="n">
+        <v>40.509559197114</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-32.1358652529169</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="b">
+        <v>0</v>
+      </c>
+      <c r="R32" t="b">
         <v>1</v>
       </c>
-      <c r="R32" t="b">
-        <v>0</v>
-      </c>
       <c r="S32" t="b">
         <v>0</v>
       </c>
       <c r="T32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>pesar celulosa; falta familia</t>
+          <t>pesar bulk</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>p68-8869</t>
+          <t>p74-8832</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -16546,572 +16336,6 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>2199</v>
-      </c>
-      <c r="B33" t="n">
-        <v>8893</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Moraceae</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Pseudolmedia</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>macrophylla</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>3855</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>69</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I33" t="n">
-        <v>8893</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>43.4988316896495</v>
-      </c>
-      <c r="L33" t="n">
-        <v>-33.7079403532742</v>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="b">
-        <v>0</v>
-      </c>
-      <c r="R33" t="b">
-        <v>1</v>
-      </c>
-      <c r="S33" t="b">
-        <v>0</v>
-      </c>
-      <c r="T33" t="b">
-        <v>0</v>
-      </c>
-      <c r="U33" t="b">
-        <v>0</v>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>pesar bulk</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>69-8893</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="n">
-        <v>8617</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="n">
-        <v>69</v>
-      </c>
-      <c r="H34" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="n">
-        <v>42.5482890591904</v>
-      </c>
-      <c r="L34" t="n">
-        <v>-30.1388182040637</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.01853964833900083</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.4430114955907127</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="P34" t="n">
-        <v>-32.61</v>
-      </c>
-      <c r="Q34" t="b">
-        <v>0</v>
-      </c>
-      <c r="R34" t="b">
-        <v>0</v>
-      </c>
-      <c r="S34" t="b">
-        <v>0</v>
-      </c>
-      <c r="T34" t="b">
-        <v>1</v>
-      </c>
-      <c r="U34" t="b">
-        <v>1</v>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>falta familia</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>p69-8617</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>p69-8617</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>2239</v>
-      </c>
-      <c r="B35" t="n">
-        <v>3643</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Melastomataceae</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Miconia</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="n">
-        <v>3899</v>
-      </c>
-      <c r="G35" t="n">
-        <v>70</v>
-      </c>
-      <c r="H35" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I35" t="n">
-        <v>3643</v>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="n">
-        <v>46.0901105921165</v>
-      </c>
-      <c r="L35" t="n">
-        <v>-31.501955307122</v>
-      </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="b">
-        <v>0</v>
-      </c>
-      <c r="R35" t="b">
-        <v>1</v>
-      </c>
-      <c r="S35" t="b">
-        <v>0</v>
-      </c>
-      <c r="T35" t="b">
-        <v>0</v>
-      </c>
-      <c r="U35" t="b">
-        <v>1</v>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>pesar bulk</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>70-3643</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="n">
-        <v>3645</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Salicacia</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Laetia</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="n">
-        <v>70</v>
-      </c>
-      <c r="H36" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
-        <v>42.6221781327326</v>
-      </c>
-      <c r="L36" t="n">
-        <v>-33.053099414117</v>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="b">
-        <v>0</v>
-      </c>
-      <c r="R36" t="b">
-        <v>1</v>
-      </c>
-      <c r="S36" t="b">
-        <v>0</v>
-      </c>
-      <c r="T36" t="b">
-        <v>0</v>
-      </c>
-      <c r="U36" t="b">
-        <v>1</v>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>pesar bulk</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>p70-3645</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="n">
-        <v>3650</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>indet</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="n">
-        <v>70</v>
-      </c>
-      <c r="H37" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="n">
-        <v>42.13</v>
-      </c>
-      <c r="L37" t="n">
-        <v>-31.61</v>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R37" t="b">
-        <v>1</v>
-      </c>
-      <c r="S37" t="b">
-        <v>0</v>
-      </c>
-      <c r="T37" t="b">
-        <v>0</v>
-      </c>
-      <c r="U37" t="b">
-        <v>1</v>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>pesar bulk</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>p70-3650</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>3643</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="n">
-        <v>70</v>
-      </c>
-      <c r="H38" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="n">
-        <v>0.02072311918279543</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0.4566504070584768</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2.193788836234638</v>
-      </c>
-      <c r="P38" t="n">
-        <v>-33.15107748731418</v>
-      </c>
-      <c r="Q38" t="b">
-        <v>1</v>
-      </c>
-      <c r="R38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T38" t="b">
-        <v>1</v>
-      </c>
-      <c r="U38" t="b">
-        <v>1</v>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>pesar celulosa; falta familia</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>p70-3643</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>8893</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="n">
-        <v>72</v>
-      </c>
-      <c r="H39" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="n">
-        <v>0.0140003582445462</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.3883734423353893</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0.8692445291019997</v>
-      </c>
-      <c r="P39" t="n">
-        <v>-35.5916730458568</v>
-      </c>
-      <c r="Q39" t="b">
-        <v>1</v>
-      </c>
-      <c r="R39" t="b">
-        <v>0</v>
-      </c>
-      <c r="S39" t="b">
-        <v>0</v>
-      </c>
-      <c r="T39" t="b">
-        <v>1</v>
-      </c>
-      <c r="U39" t="b">
-        <v>1</v>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>pesar celulosa; falta familia</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>p72-8893</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>2393</v>
-      </c>
-      <c r="B40" t="n">
-        <v>8832</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Violaceae</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Leonia</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>longifolium</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>3270</v>
-      </c>
-      <c r="G40" t="n">
-        <v>74</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="n">
-        <v>40.509559197114</v>
-      </c>
-      <c r="L40" t="n">
-        <v>-32.1358652529169</v>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="b">
-        <v>0</v>
-      </c>
-      <c r="R40" t="b">
-        <v>1</v>
-      </c>
-      <c r="S40" t="b">
-        <v>0</v>
-      </c>
-      <c r="T40" t="b">
-        <v>0</v>
-      </c>
-      <c r="U40" t="b">
-        <v>0</v>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>pesar bulk</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>p74-8832</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17207,22 +16431,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Selva Viva/celulosa_bulk_final.xlsx
+++ b/Selva Viva/celulosa_bulk_final.xlsx
@@ -8614,52 +8614,58 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="B91" t="n">
-        <v>8889</v>
+        <v>8865</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Euphorbiaceae</t>
+          <t>Violaceae</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Pseudosenefeldera</t>
+          <t>Leonia</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>inclinata</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
+          <t>glycycarpa</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>3928</t>
+        </is>
+      </c>
       <c r="G91" t="n">
         <v>68</v>
       </c>
       <c r="H91" t="n">
         <v>2025</v>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="n">
+        <v>9865</v>
+      </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="n">
-        <v>41.9886199891232</v>
+        <v>50.7386705764376</v>
       </c>
       <c r="L91" t="n">
-        <v>-30.4633399452444</v>
+        <v>-32.9258451761764</v>
       </c>
       <c r="M91" t="n">
-        <v>0.024841004</v>
+        <v>0.02234992814914083</v>
       </c>
       <c r="N91" t="n">
-        <v>0.404913041</v>
+        <v>0.4489033340843991</v>
       </c>
       <c r="O91" t="n">
-        <v>1.312047979797978</v>
+        <v>2.108676665915091</v>
       </c>
       <c r="P91" t="n">
-        <v>-31.78777476139979</v>
+        <v>-33.46661356502295</v>
       </c>
       <c r="Q91" t="b">
         <v>0</v>
@@ -8683,7 +8689,7 @@
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>p68-8889</t>
+          <t>p68-8865</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
@@ -8691,40 +8697,32 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>p68-8889</t>
-        </is>
-      </c>
+      <c r="Y91" t="inlineStr"/>
       <c r="Z91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="B92" t="n">
-        <v>8888</v>
+        <v>8889</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Simaroubaceae</t>
+          <t>Euphorbiaceae</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Simaba</t>
+          <t>Pseudosenefeldera</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>polyphylla</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>3929</t>
-        </is>
-      </c>
+          <t>inclinata</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
         <v>68</v>
       </c>
@@ -8734,22 +8732,22 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="n">
-        <v>45.0545859187322</v>
+        <v>41.9886199891232</v>
       </c>
       <c r="L92" t="n">
-        <v>-33.0441162369113</v>
+        <v>-30.4633399452444</v>
       </c>
       <c r="M92" t="n">
-        <v>0.011420399</v>
+        <v>0.024841004</v>
       </c>
       <c r="N92" t="n">
-        <v>0.430948024</v>
+        <v>0.404913041</v>
       </c>
       <c r="O92" t="n">
-        <v>2.435300505050503</v>
+        <v>1.312047979797978</v>
       </c>
       <c r="P92" t="n">
-        <v>-34.86093531283139</v>
+        <v>-31.78777476139979</v>
       </c>
       <c r="Q92" t="b">
         <v>0</v>
@@ -8773,7 +8771,7 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>p68-8888</t>
+          <t>p68-8889</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
@@ -8783,36 +8781,36 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>p68-8888</t>
+          <t>p68-8889</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2154</v>
+        <v>2148</v>
       </c>
       <c r="B93" t="n">
-        <v>8885</v>
+        <v>8888</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Apocynaceae</t>
+          <t>Simaroubaceae</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Aspidosperma</t>
+          <t>Simaba</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>aff. excelsum</t>
+          <t>polyphylla</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -8823,22 +8821,26 @@
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
+      <c r="K93" t="n">
+        <v>45.0545859187322</v>
+      </c>
+      <c r="L93" t="n">
+        <v>-33.0441162369113</v>
+      </c>
       <c r="M93" t="n">
-        <v>0.015294916</v>
+        <v>0.011420399</v>
       </c>
       <c r="N93" t="n">
-        <v>0.488282508</v>
+        <v>0.430948024</v>
       </c>
       <c r="O93" t="n">
-        <v>0.8692272727272705</v>
+        <v>2.435300505050503</v>
       </c>
       <c r="P93" t="n">
-        <v>-33.91217433722163</v>
+        <v>-34.86093531283139</v>
       </c>
       <c r="Q93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R93" t="b">
         <v>0</v>
@@ -8854,12 +8856,12 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>pesar celulosa</t>
+          <t>completo</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>p68-8885</t>
+          <t>p68-8888</t>
         </is>
       </c>
       <c r="X93" t="inlineStr">
@@ -8869,152 +8871,172 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>p68-8885</t>
+          <t>p68-8888</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
+        <v>2154</v>
+      </c>
+      <c r="B94" t="n">
+        <v>8885</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Apocynaceae</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Aspidosperma</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>aff. excelsum</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>3921</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>68</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2025</v>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="n">
+        <v>0.015294916</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.488282508</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.8692272727272705</v>
+      </c>
+      <c r="P94" t="n">
+        <v>-33.91217433722163</v>
+      </c>
+      <c r="Q94" t="b">
+        <v>1</v>
+      </c>
+      <c r="R94" t="b">
+        <v>0</v>
+      </c>
+      <c r="S94" t="b">
+        <v>0</v>
+      </c>
+      <c r="T94" t="b">
+        <v>0</v>
+      </c>
+      <c r="U94" t="b">
+        <v>0</v>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>pesar celulosa</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>p68-8885</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>p68-8885</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
         <v>2155</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B95" t="n">
         <v>8883</v>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Melastomataceae</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>Miconia</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>sp</t>
         </is>
       </c>
-      <c r="F94">
+      <c r="F95">
         <f>3899</f>
         <v/>
       </c>
-      <c r="G94" t="n">
-        <v>68</v>
-      </c>
-      <c r="H94" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="n">
-        <v>40.9764178729058</v>
-      </c>
-      <c r="L94" t="n">
-        <v>-30.0244515471261</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0.014952077</v>
-      </c>
-      <c r="N94" t="n">
-        <v>0.406260288</v>
-      </c>
-      <c r="O94" t="n">
-        <v>2.392098484848483</v>
-      </c>
-      <c r="P94" t="n">
-        <v>-31.90121357370095</v>
-      </c>
-      <c r="Q94" t="b">
-        <v>0</v>
-      </c>
-      <c r="R94" t="b">
-        <v>0</v>
-      </c>
-      <c r="S94" t="b">
-        <v>0</v>
-      </c>
-      <c r="T94" t="b">
-        <v>0</v>
-      </c>
-      <c r="U94" t="b">
-        <v>0</v>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>completo</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>p68-8883</t>
-        </is>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>p68-8883</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-      <c r="B95" t="n">
-        <v>8640</v>
-      </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
         <v>68</v>
       </c>
       <c r="H95" t="n">
         <v>2025</v>
       </c>
-      <c r="I95" t="n">
-        <v>8640</v>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="n">
-        <v>44.8257164326167</v>
+        <v>40.9764178729058</v>
       </c>
       <c r="L95" t="n">
-        <v>-27.3770370113265</v>
-      </c>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
+        <v>-30.0244515471261</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.014952077</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.406260288</v>
+      </c>
+      <c r="O95" t="n">
+        <v>2.392098484848483</v>
+      </c>
+      <c r="P95" t="n">
+        <v>-31.90121357370095</v>
+      </c>
       <c r="Q95" t="b">
         <v>0</v>
       </c>
       <c r="R95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S95" t="b">
         <v>0</v>
       </c>
       <c r="T95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>pesar bulk; falta familia</t>
+          <t>completo</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>p68-8640</t>
+          <t>p68-8883</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
@@ -9022,13 +9044,17 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>p68-8883</t>
+        </is>
+      </c>
       <c r="Z95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>8865</v>
+        <v>8640</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
@@ -9041,32 +9067,24 @@
         <v>2025</v>
       </c>
       <c r="I96" t="n">
-        <v>9865</v>
+        <v>8640</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="n">
-        <v>50.7386705764376</v>
+        <v>44.8257164326167</v>
       </c>
       <c r="L96" t="n">
-        <v>-32.9258451761764</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0.02234992814914083</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0.4489033340843991</v>
-      </c>
-      <c r="O96" t="n">
-        <v>2.108676665915091</v>
-      </c>
-      <c r="P96" t="n">
-        <v>-33.46661356502295</v>
-      </c>
+        <v>-27.3770370113265</v>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
       <c r="Q96" t="b">
         <v>0</v>
       </c>
       <c r="R96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S96" t="b">
         <v>0</v>
@@ -9079,12 +9097,12 @@
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>falta familia</t>
+          <t>pesar bulk; falta familia</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>p68-8865</t>
+          <t>p68-8640</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
@@ -13678,7 +13696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z32"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16062,63 +16080,61 @@
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>8865</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+        <v>3645</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Salicacia</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Laetia</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H29" t="n">
         <v>2025</v>
       </c>
-      <c r="I29" t="n">
-        <v>9865</v>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
-        <v>50.7386705764376</v>
+        <v>42.6221781327326</v>
       </c>
       <c r="L29" t="n">
-        <v>-32.9258451761764</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.02234992814914083</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.4489033340843991</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.108676665915091</v>
-      </c>
-      <c r="P29" t="n">
-        <v>-33.46661356502295</v>
-      </c>
+        <v>-33.053099414117</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="b">
         <v>0</v>
       </c>
       <c r="R29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="b">
         <v>0</v>
       </c>
       <c r="T29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="b">
         <v>1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>falta familia</t>
+          <t>pesar bulk</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>p68-8865</t>
+          <t>p70-3645</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -16132,18 +16148,14 @@
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>3645</v>
+        <v>3650</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Salicacia</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Laetia</t>
-        </is>
-      </c>
+          <t>indet</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
@@ -16155,10 +16167,10 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
-        <v>42.6221781327326</v>
+        <v>42.13</v>
       </c>
       <c r="L30" t="n">
-        <v>-33.053099414117</v>
+        <v>-31.61</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -16186,7 +16198,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>p70-3645</t>
+          <t>p70-3650</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -16198,20 +16210,32 @@
       <c r="Z30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="n">
+        <v>2393</v>
+      </c>
       <c r="B31" t="n">
-        <v>3650</v>
+        <v>8832</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>indet</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+          <t>Violaceae</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Leonia</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>longifolium</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3270</v>
+      </c>
       <c r="G31" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H31" t="n">
         <v>2025</v>
@@ -16219,10 +16243,10 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="n">
-        <v>42.13</v>
+        <v>40.509559197114</v>
       </c>
       <c r="L31" t="n">
-        <v>-31.61</v>
+        <v>-32.1358652529169</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -16241,7 +16265,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -16250,7 +16274,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>p70-3650</t>
+          <t>p74-8832</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -16260,82 +16284,6 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>2393</v>
-      </c>
-      <c r="B32" t="n">
-        <v>8832</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Violaceae</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Leonia</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>longifolium</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>3270</v>
-      </c>
-      <c r="G32" t="n">
-        <v>74</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
-        <v>40.509559197114</v>
-      </c>
-      <c r="L32" t="n">
-        <v>-32.1358652529169</v>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="b">
-        <v>0</v>
-      </c>
-      <c r="R32" t="b">
-        <v>1</v>
-      </c>
-      <c r="S32" t="b">
-        <v>0</v>
-      </c>
-      <c r="T32" t="b">
-        <v>0</v>
-      </c>
-      <c r="U32" t="b">
-        <v>0</v>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>pesar bulk</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>p74-8832</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16443,10 +16391,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
